--- a/source/09_GenerativeAI_RPA/genai_rpa.xlsx
+++ b/source/09_GenerativeAI_RPA/genai_rpa.xlsx
@@ -1,46 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GenAI_RPA\source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai_x\source\09_GenerativeAI_RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{04EFD337-FD45-44EB-8F05-A1C6B6A4A50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-40" yWindow="-40" windowWidth="25680" windowHeight="13760" activeTab="3"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="origin_report" sheetId="26" r:id="rId1"/>
     <sheet name="prev_report" sheetId="202" r:id="rId2"/>
     <sheet name="now_report" sheetId="205" r:id="rId3"/>
     <sheet name="now_report_en" sheetId="206" r:id="rId4"/>
-    <sheet name="prev_list" sheetId="201" r:id="rId5"/>
-    <sheet name="now_list" sheetId="204" r:id="rId6"/>
+    <sheet name="now_list" sheetId="204" r:id="rId5"/>
+    <sheet name="prev_list" sheetId="207" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="208">
   <si>
     <t>OOO 일일 동향 보고서</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -463,11 +453,239 @@
 On March 21, 2025, Olga Whole Foods announced its foray into the healthy snack market, focusing on domestic health products. With an increasing consumer demand for nutritious food options, Olga aims to leverage locally sourced ingredients to create a diverse range of snacks. This initiative aligns with the global trend of growing health consciousness, particularly among younger generations. The company plans to launch its first line of products by the end of April 2025, anticipating a significant response from health-oriented consumers. As competitors in the market intensify, Olga Whole Foods seeks to distinguish itself by emphasizing the quality and provenance of its ingredients, ensuring a strong position in this competitive segment.
 </t>
   </si>
+  <si>
+    <t>75g 덴티 &lt;b&gt;포켄스&lt;/b&gt; 페어리 L D18 IWFI7HAK</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043101733</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958761/89587612432.jpg</t>
+  </si>
+  <si>
+    <t>도매도매24</t>
+  </si>
+  <si>
+    <t>강아지 간식</t>
+  </si>
+  <si>
+    <t>개껌</t>
+  </si>
+  <si>
+    <t>입냄새감소 치석 애견껌 카누들 &lt;b&gt;포켄스&lt;/b&gt; 플러스S 60p CWF88C98</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043250896</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958776/89587761595.jpg</t>
+  </si>
+  <si>
+    <t>로얄하이츠</t>
+  </si>
+  <si>
+    <t>포비스 3in1 샴푸n린스 1000ml</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043207487</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958771/89587718186.jpg</t>
+  </si>
+  <si>
+    <t>gulink</t>
+  </si>
+  <si>
+    <t>포켄스</t>
+  </si>
+  <si>
+    <t>간식 후레시 강아지 칼슘 큰별 220g &lt;b&gt;포켄스&lt;/b&gt; 덴탈스틱</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043196089</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958770/89587706788.jpg</t>
+  </si>
+  <si>
+    <t>에코플렉스s</t>
+  </si>
+  <si>
+    <t>블루베리 큰별 후레시 &lt;b&gt;포켄스&lt;/b&gt; 220g 개껌 D18 덴탈스틱 NWFI7HA5</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043170721</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958768/89587681417.jpg</t>
+  </si>
+  <si>
+    <t>거성에테르</t>
+  </si>
+  <si>
+    <t>EXTREMO 우리 애기 &lt;b&gt;FORCANS&lt;/b&gt; 과일먹은 치즈덴탈껌 100g 9개세트</t>
+  </si>
+  <si>
+    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=7186993419&amp;tid=1000000061</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557838/55578388953.jpg</t>
+  </si>
+  <si>
+    <t>EXTREMO 우리 애기 &lt;b&gt;FORCANS&lt;/b&gt; DENTAL STICK 오메가3 M 큰별 220g</t>
+  </si>
+  <si>
+    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=7186993417&amp;tid=1000000061</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557837/55578379444.jpg</t>
+  </si>
+  <si>
+    <t>EXTREMO 우리 애기 &lt;b&gt;FORCANS&lt;/b&gt; DENTAL STICK 블루베리 M 220g</t>
+  </si>
+  <si>
+    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=7186993409&amp;tid=1000000061</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557834/55578340707.jpg</t>
+  </si>
+  <si>
+    <t>EXTREMO 우리 애기 &lt;b&gt;FORCANS&lt;/b&gt; DENTAL STICK 블루베리 S 220g</t>
+  </si>
+  <si>
+    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=7186993414&amp;tid=1000000061</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557832/55578326006.jpg</t>
+  </si>
+  <si>
+    <t>65g &lt;b&gt;포켄스&lt;/b&gt; D18 SS 덴티 페어리 OWFI7HAP</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043122423</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958763/89587633120.jpg</t>
+  </si>
+  <si>
+    <t>애견 개껌 반려견 100g 사과 &lt;b&gt;포켄스&lt;/b&gt; 간식 치즈덴탈껌 EW485B12</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043101155</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958761/89587611854.jpg</t>
+  </si>
+  <si>
+    <t>(M) 간식) (강아지 덴티 &lt;b&gt;포켄스&lt;/b&gt; 페어리 75g</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043079755</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958759/89587590454.jpg</t>
+  </si>
+  <si>
+    <t>윤댕쁘띠</t>
+  </si>
+  <si>
+    <t>덴티 &lt;b&gt;포켄스&lt;/b&gt; 간식) (강아지 65g (SS) 페어리</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043079293</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958758/89587589992.jpg</t>
+  </si>
+  <si>
+    <t>(L) &lt;b&gt;포켄스&lt;/b&gt; 75g 간식) (강아지 페어리 덴티</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043079518</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958759/89587590217.jpg</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;포켄스&lt;/b&gt; 덴티 간식) 페어리 (S) 65g (강아지</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043079088</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958758/89587589787.jpg</t>
+  </si>
+  <si>
+    <t>후레시 220g 개껌 D18 칼슘 &lt;b&gt;포켄스&lt;/b&gt; 큰별 덴탈스틱 PWFI7H9Y</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12042994000</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958750/89587504699.jpg</t>
+  </si>
+  <si>
+    <t>하니스토어20</t>
+  </si>
+  <si>
+    <t>냄새 감염방지 강아지 귀 청소 세정제 건강관리용품 포메귀</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12042959001</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958746/89587469700.jpg</t>
+  </si>
+  <si>
+    <t>무배의민족</t>
+  </si>
+  <si>
+    <t>더키코</t>
+  </si>
+  <si>
+    <t>강아지 건강/관리용품</t>
+  </si>
+  <si>
+    <t>눈/귀 관리용품</t>
+  </si>
+  <si>
+    <t>입냄새제거 이빨 잇몸 위생 애견 입 스프레이 뿌리는치약 여행</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12042958765</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958746/89587469464.jpg</t>
+  </si>
+  <si>
+    <t>구강청결제</t>
+  </si>
+  <si>
+    <t>달콤한 딸기향 치석제거 강아지 먹는 치약 입냄새감소 위생용품</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12042958165</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958746/89587468864.jpg</t>
+  </si>
+  <si>
+    <t>입냄새제거 이빨 잇몸 위생 애견 입 스프레이 간편함 포메구강</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12042898502</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958740/89587409201.jpg</t>
+  </si>
+  <si>
+    <t>라이크미리빙</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -905,39 +1123,39 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="85.58203125" customWidth="1"/>
+    <col min="1" max="1" width="85.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="36" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" ht="36" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="4"/>
     </row>
-    <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="1:1" ht="21" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="7" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:1" s="3" customFormat="1" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:1" s="3" customFormat="1" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A8" s="5"/>
     </row>
   </sheetData>
@@ -948,43 +1166,43 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="85.58203125" customWidth="1"/>
+    <col min="1" max="1" width="85.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="36" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" ht="36" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="350" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" ht="384" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="1:1" ht="21" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="7" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:1" s="3" customFormat="1" ht="157.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:1" s="3" customFormat="1" ht="172.8" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
         <v>122</v>
       </c>
@@ -997,43 +1215,43 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="85.58203125" customWidth="1"/>
+    <col min="1" max="1" width="85.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="36" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" ht="36" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="367.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" ht="403.2" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="1:1" ht="21" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="7" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:1" s="3" customFormat="1" ht="157.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:1" s="3" customFormat="1" ht="172.8" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
         <v>130</v>
       </c>
@@ -1046,43 +1264,43 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="85.58203125" customWidth="1"/>
+    <col min="1" max="1" width="85.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="36" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" ht="36" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="7" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="350" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" ht="384" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="1:1" ht="21" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="7" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="8" spans="1:1" s="3" customFormat="1" ht="210" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:1" s="3" customFormat="1" ht="230.4" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
         <v>131</v>
       </c>
@@ -1095,11 +1313,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:O21"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1146,27 +1364,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="E2">
-        <v>23920</v>
+        <v>6810</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="H2">
-        <v>53858743882</v>
+        <v>89587612432</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -1175,36 +1393,36 @@
         <v>20</v>
       </c>
       <c r="M2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N2" t="s">
-        <v>28</v>
+        <v>136</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>138</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="E3">
-        <v>17020</v>
+        <v>34200</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="H3">
-        <v>53858734010</v>
+        <v>89587761595</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -1213,112 +1431,118 @@
         <v>20</v>
       </c>
       <c r="M3" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>47</v>
+        <v>136</v>
       </c>
       <c r="O3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>144</v>
       </c>
       <c r="E4">
-        <v>57890</v>
+        <v>16770</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="H4">
-        <v>53858727893</v>
+        <v>89587718186</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
+      <c r="J4" t="s">
+        <v>146</v>
+      </c>
+      <c r="K4" t="s">
+        <v>146</v>
+      </c>
       <c r="L4" t="s">
         <v>20</v>
       </c>
       <c r="M4" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="N4" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="O4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>147</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>148</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="E5">
-        <v>2970</v>
+        <v>15920</v>
       </c>
       <c r="G5" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="H5">
-        <v>53858722011</v>
+        <v>89587706788</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="L5" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="M5" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="N5" t="s">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="O5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>151</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>153</v>
       </c>
       <c r="E6">
-        <v>28130</v>
+        <v>13360</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="H6">
-        <v>53858696356</v>
+        <v>89587681417</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -1327,45 +1551,39 @@
         <v>20</v>
       </c>
       <c r="M6" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="N6" t="s">
-        <v>47</v>
+        <v>136</v>
       </c>
       <c r="O6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>157</v>
       </c>
       <c r="E7">
-        <v>31400</v>
+        <v>56080</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="H7">
-        <v>89200019767</v>
+        <v>55578388953</v>
       </c>
       <c r="I7">
         <v>2</v>
-      </c>
-      <c r="J7" t="s">
-        <v>34</v>
-      </c>
-      <c r="K7" t="s">
-        <v>34</v>
       </c>
       <c r="L7" t="s">
         <v>20</v>
@@ -1374,33 +1592,33 @@
         <v>21</v>
       </c>
       <c r="N7" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="O7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>160</v>
       </c>
       <c r="E8">
-        <v>49300</v>
+        <v>19960</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="H8">
-        <v>89199968681</v>
+        <v>55578379444</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -1412,30 +1630,33 @@
         <v>21</v>
       </c>
       <c r="N8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+        <v>136</v>
+      </c>
+      <c r="O8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>161</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>162</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>163</v>
       </c>
       <c r="E9">
-        <v>47500</v>
+        <v>19960</v>
       </c>
       <c r="G9" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="H9">
-        <v>53858651732</v>
+        <v>55578340707</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -1447,33 +1668,33 @@
         <v>21</v>
       </c>
       <c r="N9" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="O9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>164</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>165</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>166</v>
       </c>
       <c r="E10">
-        <v>17000</v>
+        <v>19010</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="H10">
-        <v>53858622401</v>
+        <v>55578326006</v>
       </c>
       <c r="I10">
         <v>2</v>
@@ -1482,36 +1703,36 @@
         <v>20</v>
       </c>
       <c r="M10" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N10" t="s">
-        <v>28</v>
+        <v>136</v>
       </c>
       <c r="O10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>167</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>169</v>
       </c>
       <c r="E11">
-        <v>20430</v>
+        <v>6800</v>
       </c>
       <c r="G11" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="H11">
-        <v>89199897770</v>
+        <v>89587633120</v>
       </c>
       <c r="I11">
         <v>2</v>
@@ -1523,33 +1744,33 @@
         <v>21</v>
       </c>
       <c r="N11" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="O11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>171</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="E12">
-        <v>19300</v>
+        <v>4160</v>
       </c>
       <c r="G12" t="s">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="H12">
-        <v>89199841858</v>
+        <v>89587611854</v>
       </c>
       <c r="I12">
         <v>2</v>
@@ -1561,74 +1782,80 @@
         <v>21</v>
       </c>
       <c r="N12" t="s">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="O12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>175</v>
       </c>
       <c r="E13">
-        <v>11400</v>
+        <v>12750</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>176</v>
       </c>
       <c r="H13">
-        <v>53858521678</v>
+        <v>89587590454</v>
       </c>
       <c r="I13">
         <v>2</v>
       </c>
+      <c r="K13" t="s">
+        <v>146</v>
+      </c>
       <c r="L13" t="s">
         <v>20</v>
       </c>
       <c r="M13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N13" t="s">
-        <v>28</v>
+        <v>136</v>
       </c>
       <c r="O13" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>177</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>178</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>179</v>
       </c>
       <c r="E14">
-        <v>79990</v>
+        <v>12750</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
+        <v>176</v>
       </c>
       <c r="H14">
-        <v>53858391642</v>
+        <v>89587589992</v>
       </c>
       <c r="I14">
         <v>2</v>
+      </c>
+      <c r="K14" t="s">
+        <v>146</v>
       </c>
       <c r="L14" t="s">
         <v>20</v>
@@ -1637,39 +1864,39 @@
         <v>21</v>
       </c>
       <c r="N14" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="O14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>180</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>181</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>182</v>
       </c>
       <c r="E15">
-        <v>28340</v>
+        <v>12750</v>
       </c>
       <c r="G15" t="s">
-        <v>18</v>
+        <v>176</v>
       </c>
       <c r="H15">
-        <v>53858387095</v>
+        <v>89587590217</v>
       </c>
       <c r="I15">
         <v>2</v>
       </c>
       <c r="K15" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="L15" t="s">
         <v>20</v>
@@ -1678,71 +1905,74 @@
         <v>21</v>
       </c>
       <c r="N15" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="O15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>183</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>184</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="E16">
-        <v>42670</v>
+        <v>12750</v>
       </c>
       <c r="G16" t="s">
-        <v>18</v>
+        <v>176</v>
       </c>
       <c r="H16">
-        <v>53858324859</v>
+        <v>89587589787</v>
       </c>
       <c r="I16">
         <v>2</v>
       </c>
+      <c r="K16" t="s">
+        <v>146</v>
+      </c>
       <c r="L16" t="s">
         <v>20</v>
       </c>
       <c r="M16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N16" t="s">
-        <v>28</v>
+        <v>136</v>
       </c>
       <c r="O16" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>186</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>187</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>188</v>
       </c>
       <c r="E17">
-        <v>33870</v>
+        <v>13350</v>
       </c>
       <c r="G17" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="H17">
-        <v>53858287681</v>
+        <v>89587504699</v>
       </c>
       <c r="I17">
         <v>2</v>
@@ -1751,39 +1981,45 @@
         <v>20</v>
       </c>
       <c r="M17" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="N17" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="O17" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>191</v>
       </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>192</v>
       </c>
       <c r="E18">
-        <v>38029</v>
+        <v>10710</v>
       </c>
       <c r="G18" t="s">
-        <v>58</v>
+        <v>193</v>
       </c>
       <c r="H18">
-        <v>53858277897</v>
+        <v>89587469700</v>
       </c>
       <c r="I18">
         <v>2</v>
+      </c>
+      <c r="J18" t="s">
+        <v>194</v>
+      </c>
+      <c r="K18" t="s">
+        <v>146</v>
       </c>
       <c r="L18" t="s">
         <v>20</v>
@@ -1792,74 +2028,86 @@
         <v>21</v>
       </c>
       <c r="N18" t="s">
-        <v>103</v>
+        <v>195</v>
       </c>
       <c r="O18" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>197</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>198</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>199</v>
       </c>
       <c r="E19">
-        <v>11100</v>
+        <v>10710</v>
       </c>
       <c r="G19" t="s">
-        <v>96</v>
+        <v>193</v>
       </c>
       <c r="H19">
-        <v>53858271216</v>
+        <v>89587469464</v>
       </c>
       <c r="I19">
         <v>2</v>
       </c>
+      <c r="J19" t="s">
+        <v>194</v>
+      </c>
+      <c r="K19" t="s">
+        <v>146</v>
+      </c>
       <c r="L19" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="M19" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="N19" t="s">
-        <v>108</v>
+        <v>195</v>
       </c>
       <c r="O19" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>201</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>202</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>203</v>
       </c>
       <c r="E20">
-        <v>17150</v>
+        <v>10710</v>
       </c>
       <c r="G20" t="s">
-        <v>113</v>
+        <v>193</v>
       </c>
       <c r="H20">
-        <v>89199782272</v>
+        <v>89587468864</v>
       </c>
       <c r="I20">
         <v>2</v>
+      </c>
+      <c r="J20" t="s">
+        <v>194</v>
+      </c>
+      <c r="K20" t="s">
+        <v>146</v>
       </c>
       <c r="L20" t="s">
         <v>20</v>
@@ -1868,48 +2116,54 @@
         <v>21</v>
       </c>
       <c r="N20" t="s">
-        <v>22</v>
+        <v>195</v>
       </c>
       <c r="O20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>204</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="D21" t="s">
-        <v>116</v>
+        <v>206</v>
       </c>
       <c r="E21">
-        <v>30010</v>
+        <v>7200</v>
       </c>
       <c r="G21" t="s">
-        <v>117</v>
+        <v>207</v>
       </c>
       <c r="H21">
-        <v>89199782212</v>
+        <v>89587409201</v>
       </c>
       <c r="I21">
         <v>2</v>
       </c>
+      <c r="J21" t="s">
+        <v>194</v>
+      </c>
+      <c r="K21" t="s">
+        <v>146</v>
+      </c>
       <c r="L21" t="s">
         <v>20</v>
       </c>
       <c r="M21" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="N21" t="s">
-        <v>118</v>
+        <v>195</v>
       </c>
       <c r="O21" t="s">
-        <v>119</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -1919,11 +2173,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FD1B9B7-CABE-4891-9949-9276C745F61B}">
   <dimension ref="A1:O21"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1970,7 +2224,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2008,7 +2262,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2046,7 +2300,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2084,7 +2338,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2122,7 +2376,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2160,7 +2414,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2204,7 +2458,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2239,7 +2493,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2277,7 +2531,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2315,7 +2569,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2353,7 +2607,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2391,7 +2645,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2429,7 +2683,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2467,7 +2721,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2508,7 +2762,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2546,7 +2800,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2584,7 +2838,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2622,7 +2876,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2660,7 +2914,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2698,7 +2952,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>20</v>
       </c>

--- a/source/09_GenerativeAI_RPA/genai_rpa.xlsx
+++ b/source/09_GenerativeAI_RPA/genai_rpa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai_x\source\09_GenerativeAI_RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04EFD337-FD45-44EB-8F05-A1C6B6A4A50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF975919-C5EF-4145-987F-01D3FA180644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="now_report" sheetId="205" r:id="rId3"/>
     <sheet name="now_report_en" sheetId="206" r:id="rId4"/>
     <sheet name="now_list" sheetId="204" r:id="rId5"/>
-    <sheet name="prev_list" sheetId="207" r:id="rId6"/>
+    <sheet name="prev_list" sheetId="208" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="198">
   <si>
     <t>OOO 일일 동향 보고서</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -89,12 +89,6 @@
     <t>category4</t>
   </si>
   <si>
-    <t>쿠팡</t>
-  </si>
-  <si>
-    <t>옥션</t>
-  </si>
-  <si>
     <t>생활/건강</t>
   </si>
   <si>
@@ -107,292 +101,16 @@
     <t>샴푸/린스/비누</t>
   </si>
   <si>
-    <t>개 대 정장 샴푸 프레스 대비누대 비누 블랙 치솔 칫솔 세트 플라스틱 욕실 치솔꽂이</t>
-  </si>
-  <si>
-    <t>https://link.auction.co.kr/gate/pcs?item-no=E946603010&amp;sub-id=1&amp;service-code=10000003</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385874/53858743882.jpg</t>
-  </si>
-  <si>
-    <t>욕실용품</t>
-  </si>
-  <si>
-    <t>욕실용기/홀더</t>
-  </si>
-  <si>
-    <t>비눗갑/홀더/받침</t>
-  </si>
-  <si>
-    <t>시리우스 강아지 발씻자 270mlx3+실리콘팁</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/11655509301</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8920001/89200019767.jpg</t>
-  </si>
-  <si>
-    <t>노마타운</t>
-  </si>
-  <si>
-    <t>시리우스</t>
-  </si>
-  <si>
     <t>기타반려동물용품</t>
   </si>
   <si>
-    <t>오구비포</t>
-  </si>
-  <si>
-    <t>가려운 피부를 위한 오트밀 개 샴푸 건조한 각질 민감성 피부 알레르기 및 가려움증을 목욕 비누</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/11655458215</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8919996/89199968681.jpg</t>
-  </si>
-  <si>
-    <t>(2세트할인) 미국 크라운로얄 바이오바이트 컨디션플러스 말티즈 꼬똥 시츄 아프간  3단모파상모이중모테리어  2개  236ml</t>
-  </si>
-  <si>
-    <t>https://link.coupang.com/re/PCSNAVERPCSDP?pageKey=7657698009&amp;ctag=7657698009&amp;lptag=V82570136419&amp;itemId=20392616548&amp;vendorItemId=82570136419&amp;spec=10305199</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385865/53858651732.jpg</t>
-  </si>
-  <si>
-    <t>스퀘어 화이트 크래프트 블랙 포장 상자 웨딩 파티 개 수제 용품 비누 선물 평면 초콜릿 10</t>
-  </si>
-  <si>
-    <t>https://link.auction.co.kr/gate/pcs?item-no=E946586220&amp;sub-id=1&amp;service-code=10000003</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385873/53858734010.jpg</t>
-  </si>
-  <si>
-    <t>공구</t>
-  </si>
-  <si>
-    <t>포장용품</t>
-  </si>
-  <si>
-    <t>선물박스</t>
-  </si>
-  <si>
-    <t>블랙 크래프트 골판지 상자 선물 공예 놀이 명함 9.2 50 종이 차 비누 개/로트 포장 5.5 4cm</t>
-  </si>
-  <si>
-    <t>https://link.auction.co.kr/gate/pcs?item-no=E946580254&amp;sub-id=1&amp;service-code=10000003</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385872/53858727893.jpg</t>
-  </si>
-  <si>
-    <t>화방용품</t>
-  </si>
-  <si>
-    <t>전문지류/미술지류</t>
-  </si>
-  <si>
-    <t>골판지</t>
-  </si>
-  <si>
-    <t>욕조에 있는 사랑스러운 프렌치 불독 캔버스 벽 예술 인쇄, 12x18인치 - 액자 없는 현대적인 욕실 장식과 비누 디스펜서, 집이나 방 장식을 위한 재미있는 개 일러스트레이션,</t>
-  </si>
-  <si>
-    <t>https://temuaffiliateprogram.pxf.io/c/5257454/1580294/18350?u=https%3A%2F%2Fwww.temu.com%2Fkr%2Fgoods.html%3Fsku_id%3D17594869875357%26goods_id%3D601100132138879%26_x_ns_catalog_id%3D10000%26_x_ns_product_id%3D17594869875357%26_x_ns_site_id%3D119%26_x_ns_ad%3d{ad}</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385872/53858722011.jpg</t>
-  </si>
-  <si>
-    <t>TEMU kr</t>
-  </si>
-  <si>
-    <t>가구/인테리어</t>
-  </si>
-  <si>
-    <t>인테리어소품</t>
-  </si>
-  <si>
-    <t>액자</t>
-  </si>
-  <si>
-    <t>퍼즐/그림/사진액자</t>
-  </si>
-  <si>
-    <t>창문형 미니 크래프트 종이 상자 포장 비누 베이커리 블랙 화이트 브라운 개 30</t>
-  </si>
-  <si>
-    <t>https://link.auction.co.kr/gate/pcs?item-no=E946621381&amp;sub-id=1&amp;service-code=10000003</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385869/53858696356.jpg</t>
-  </si>
-  <si>
-    <t>외부 금속 사인 웨스티용 장식 강아지 목욕 비누 회사 재미있는 욕실 빈티지 홈 소박한 알루미늄  1개  2. 20x30cm</t>
-  </si>
-  <si>
-    <t>https://link.coupang.com/re/PCSNAVERPCSDP?pageKey=8684133347&amp;ctag=8684133347&amp;lptag=P8684133347&amp;itemId=25159103573&amp;vendorItemId=92157151447&amp;spec=10305199</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385862/53858622401.jpg</t>
-  </si>
-  <si>
-    <t>강아지 반려견 모발보습 털엉킴 방지 컨디셔너</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/11655387304</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8919989/89199897770.jpg</t>
-  </si>
-  <si>
-    <t>유라이샵</t>
-  </si>
-  <si>
-    <t>액체 비누 디펜서 리필 욕실 디스펜서 액세서리 플라 G2518ZA 접시 럭셔리 워시 오오마사토시 250ml</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/11655331392</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8919984/89199841858.jpg</t>
-  </si>
-  <si>
-    <t>롸맘직구</t>
-  </si>
-  <si>
     <t>강아지 배변용품</t>
   </si>
   <si>
-    <t>배변봉투/집게</t>
-  </si>
-  <si>
-    <t>가능 핸드 욕실 가능한 개 디펜서 300/500ml 병 젤 샴푸 리필 비누 펌프 용기 재사용 샤워  300ml  green-4pcs  4개</t>
-  </si>
-  <si>
-    <t>https://link.coupang.com/re/PCSNAVERPCSDP?pageKey=8533463550&amp;ctag=8533463550&amp;lptag=I24397425245&amp;itemId=24397425245&amp;vendorItemId=91412310960&amp;spec=10305199</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385852/53858521678.jpg</t>
-  </si>
-  <si>
-    <t>디스펜서</t>
-  </si>
-  <si>
-    <t>미국 크라운로얄 매직터치 그루밍스프레이 포뮬라3 원액1 대 물 15 비숑 포메 셀티 단모 파상모 테리어  1개  473ml</t>
-  </si>
-  <si>
-    <t>https://link.coupang.com/re/PCSNAVERPCSDP?pageKey=7690200212&amp;ctag=7690200212&amp;lptag=V82570567170&amp;itemId=20563081160&amp;vendorItemId=82570567170&amp;spec=10305199</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385839/53858391642.jpg</t>
-  </si>
-  <si>
-    <t>반려동물 마루 코팅제 500ml</t>
-  </si>
-  <si>
-    <t>https://link.coupang.com/re/PCSNAVERPCSDP?pageKey=4320780180&amp;ctag=4320780180&amp;lptag=I25168939706&amp;itemId=25168939706&amp;vendorItemId=92186685780&amp;spec=10305199</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385838/53858387095.jpg</t>
-  </si>
-  <si>
-    <t>린레이</t>
-  </si>
-  <si>
-    <t>자동 손세정기 샤워 비오레 비누 손세정제 비둘기핸드워시 센서 세정제 White 디스펜서  콜라보레이션-강아지 스탠다드핏 +벽걸이+손 세정제  1개</t>
-  </si>
-  <si>
-    <t>https://link.coupang.com/re/PCSNAVERPCSDP?pageKey=8579277330&amp;ctag=8579277330&amp;lptag=P8579277330&amp;itemId=24865506408&amp;vendorItemId=91872499335&amp;spec=10305199</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385832/53858324859.jpg</t>
-  </si>
-  <si>
-    <t>강아지발도장 동물 고양이 강아지 발자국 아크릴 스탬프 비누 엠보싱 장 각인 수제 1PC</t>
-  </si>
-  <si>
-    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=8137345774&amp;tid=1000000061</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385828/53858287681.jpg</t>
-  </si>
-  <si>
     <t>11번가</t>
   </si>
   <si>
-    <t>문구/사무용품</t>
-  </si>
-  <si>
-    <t>스탬프/도장</t>
-  </si>
-  <si>
-    <t>스탬프</t>
-  </si>
-  <si>
-    <t>2마리의 작은 개와 2마리의 고양이를 위한 럭셔리 그레이 직사각형 애완동물 침대, 비누가 닿지 않는 바닥이 있는 슈퍼 소프트 세탁 가능한 더블 고양이 침대, 실내 사용을 위한</t>
-  </si>
-  <si>
-    <t>https://temuaffiliateprogram.pxf.io/c/5257454/1580294/18350?u=https%3A%2F%2Fwww.temu.com%2Fkr%2Fgoods.html%3Fsku_id%3D17592913576699%26goods_id%3D601099700795413%26_x_ns_catalog_id%3D10000%26_x_ns_product_id%3D17592913576699%26_x_ns_site_id%3D119%26_x_ns_ad%3d{ad}</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385827/53858277897.jpg</t>
-  </si>
-  <si>
     <t>리빙용품</t>
-  </si>
-  <si>
-    <t>쿠션/방석</t>
-  </si>
-  <si>
-    <t>크리스탈 에폭시 수지 금형 수제 석고 비누 곰팡이 천사 날강아지 모양</t>
-  </si>
-  <si>
-    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=8137406874&amp;tid=1000000061</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5385827/53858271216.jpg</t>
-  </si>
-  <si>
-    <t>아로마/캔들용품</t>
-  </si>
-  <si>
-    <t>기타아로마/캔들용품</t>
-  </si>
-  <si>
-    <t>바란스 개세정액 화이트워시 브라이트 백모용 503ml</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/11655271806</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8919978/89199782272.jpg</t>
-  </si>
-  <si>
-    <t>We-Wit</t>
-  </si>
-  <si>
-    <t>크래프트 상자 블랙 화이트 포장 판지 축제 파티 비누 개 50 선물</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/11655271746</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8919978/89199782212.jpg</t>
-  </si>
-  <si>
-    <t>nninecp</t>
-  </si>
-  <si>
-    <t>소형기계</t>
-  </si>
-  <si>
-    <t>기타소형기계</t>
   </si>
   <si>
     <t>2025-03-30 15:56:04 기준</t>
@@ -680,6 +398,258 @@
   </si>
   <si>
     <t>라이크미리빙</t>
+  </si>
+  <si>
+    <t>그물망이 부드러운 대형뜰채</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043786727</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958829/89588297426.jpg</t>
+  </si>
+  <si>
+    <t>도그다</t>
+  </si>
+  <si>
+    <t>반려동물용 펫퍼스 안구세정제 120ml</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043785504</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958829/89588296203.jpg</t>
+  </si>
+  <si>
+    <t>펫퍼스</t>
+  </si>
+  <si>
+    <t>강아지 훈련용 초크체인 1호 1P 목줄 산책 목걸이</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043785572</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958829/89588296271.jpg</t>
+  </si>
+  <si>
+    <t>그루머스</t>
+  </si>
+  <si>
+    <t>강아지 장난감/훈련</t>
+  </si>
+  <si>
+    <t>훈련용품</t>
+  </si>
+  <si>
+    <t>강아지 훈련소 훈련&lt;b&gt;용품&lt;/b&gt; 점프 반면 타일 1개 블루</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043784931</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958829/89588295630.jpg</t>
+  </si>
+  <si>
+    <t>오마이픽 스토어</t>
+  </si>
+  <si>
+    <t>강아지 &lt;b&gt;애완&lt;/b&gt;견 배변판 토일렛 화장실 민트</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043784341</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958829/89588295040.jpg</t>
+  </si>
+  <si>
+    <t>배변판</t>
+  </si>
+  <si>
+    <t>천연소나무향 톱밥(35x12x9cm)</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043784069</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958829/89588294768.jpg</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;애완&lt;/b&gt;동물 안전문 게이트 강아지 고양이 현관 &lt;b&gt;애완&lt;/b&gt;견 출입문 격리</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043783577</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958829/89588294276.jpg</t>
+  </si>
+  <si>
+    <t>오팔리네</t>
+  </si>
+  <si>
+    <t>안전문</t>
+  </si>
+  <si>
+    <t>아몬스 강아지 기저귀 애견 귀저기 초미니형 10매</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043781992</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958829/89588292691.jpg</t>
+  </si>
+  <si>
+    <t>기저귀/팬티</t>
+  </si>
+  <si>
+    <t>스텐드 식기물병 벽걸이물병 강아지 고양이 애견 &lt;b&gt;용품&lt;/b&gt; 브라운</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043781294</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958829/89588291993.jpg</t>
+  </si>
+  <si>
+    <t>메리go라운드</t>
+  </si>
+  <si>
+    <t>빌리</t>
+  </si>
+  <si>
+    <t>식기/급수기</t>
+  </si>
+  <si>
+    <t>식기/식탁</t>
+  </si>
+  <si>
+    <t>강아지 목 보호대 쿠션 애견 넥카라 깔대기 KL 아쿠아폭스(M)</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043781239</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958829/89588291938.jpg</t>
+  </si>
+  <si>
+    <t>PAT</t>
+  </si>
+  <si>
+    <t>기타 미용/목욕용품</t>
+  </si>
+  <si>
+    <t>세라믹 &lt;b&gt;애완&lt;/b&gt;동물 유골함 강아지 관 추모품 사망한 강아지용 1. Red strawberry</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043781105</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958829/89588291804.jpg</t>
+  </si>
+  <si>
+    <t>성상트레이딩16호점</t>
+  </si>
+  <si>
+    <t>서비스</t>
+  </si>
+  <si>
+    <t>장례용품</t>
+  </si>
+  <si>
+    <t>고양이 강아지 털 개털 머리카락 먼지 청소 스크래퍼</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043780910</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958829/89588291609.jpg</t>
+  </si>
+  <si>
+    <t>대형견 계단 승강기 블랙 차량계단 30 GORILLA &lt;b&gt;애완&lt;/b&gt;동물 고양이계단 쿠션 원목 보호</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043780762</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958829/89588291461.jpg</t>
+  </si>
+  <si>
+    <t>물류에세이2</t>
+  </si>
+  <si>
+    <t>계단/스텝</t>
+  </si>
+  <si>
+    <t>테비 사사미 1kg 오리가슴살 개간식 반려동물 &lt;b&gt;애완용품&lt;/b&gt; 훈련용</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043778999</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958828/89588289698.jpg</t>
+  </si>
+  <si>
+    <t>프 리 즘</t>
+  </si>
+  <si>
+    <t>육포/건조간식</t>
+  </si>
+  <si>
+    <t>와인앤쿡캣잎 흡착 브러쉬 셀프 그루밍</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043778405</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958828/89588289104.jpg</t>
+  </si>
+  <si>
+    <t>현대Hmall</t>
+  </si>
+  <si>
+    <t>교보문고</t>
+  </si>
+  <si>
+    <t>와인앤쿡수족관 인테리어 성벽 장식품</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043778134</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958828/89588288833.jpg</t>
+  </si>
+  <si>
+    <t>와인앤쿡파충류 먹이그릇 1구</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043778204</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958828/89588288903.jpg</t>
+  </si>
+  <si>
+    <t>와인앤쿡횟대 큐티 모이통 4색 컬러세트</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043777649</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958828/89588288348.jpg</t>
+  </si>
+  <si>
+    <t>똥삽 고양이 화장실 배변처리 일체형 모래삽 벤토나이 오렌지</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043585157</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958809/89588095858.jpg</t>
+  </si>
+  <si>
+    <t>고양이 배변용품</t>
+  </si>
+  <si>
+    <t>분변통/모래삽</t>
   </si>
 </sst>
 </file>
@@ -1183,7 +1153,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
-        <v>120</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
@@ -1193,7 +1163,7 @@
     </row>
     <row r="5" spans="1:1" ht="384" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -1204,7 +1174,7 @@
     </row>
     <row r="8" spans="1:1" s="3" customFormat="1" ht="172.8" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1232,7 +1202,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
-        <v>124</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
@@ -1242,7 +1212,7 @@
     </row>
     <row r="5" spans="1:1" ht="403.2" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
-        <v>127</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -1253,7 +1223,7 @@
     </row>
     <row r="8" spans="1:1" s="3" customFormat="1" ht="172.8" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
-        <v>130</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1276,33 +1246,33 @@
   <sheetData>
     <row r="1" spans="1:1" ht="36" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="7" t="s">
-        <v>125</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>126</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="384" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
-        <v>128</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="7" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>129</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:1" s="3" customFormat="1" ht="230.4" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
-        <v>131</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1314,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.4">
@@ -1369,37 +1339,34 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="E2">
-        <v>6810</v>
+        <v>4130</v>
       </c>
       <c r="G2" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="H2">
-        <v>89587612432</v>
+        <v>89588297426</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O2" t="s">
-        <v>137</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
@@ -1407,37 +1374,43 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="C3" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="E3">
-        <v>34200</v>
+        <v>8230</v>
       </c>
       <c r="G3" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="H3">
-        <v>89587761595</v>
+        <v>89588296203</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
+      <c r="J3" t="s">
+        <v>121</v>
+      </c>
+      <c r="K3" t="s">
+        <v>121</v>
+      </c>
       <c r="L3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N3" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="O3" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.4">
@@ -1445,43 +1418,40 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="E4">
-        <v>16770</v>
+        <v>13200</v>
       </c>
       <c r="G4" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="H4">
-        <v>89587718186</v>
+        <v>89588296271</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
       <c r="J4" t="s">
-        <v>146</v>
-      </c>
-      <c r="K4" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="L4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N4" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="O4" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.4">
@@ -1489,37 +1459,37 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="E5">
-        <v>15920</v>
+        <v>282100</v>
       </c>
       <c r="G5" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="H5">
-        <v>89587706788</v>
+        <v>89588295630</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="L5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N5" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="O5" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.4">
@@ -1527,37 +1497,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="C6" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="E6">
-        <v>13360</v>
+        <v>16570</v>
       </c>
       <c r="G6" t="s">
-        <v>154</v>
+        <v>117</v>
       </c>
       <c r="H6">
-        <v>89587681417</v>
+        <v>89588295040</v>
       </c>
       <c r="I6">
         <v>2</v>
       </c>
       <c r="L6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N6" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="O6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.4">
@@ -1565,37 +1535,34 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="C7" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="E7">
-        <v>56080</v>
+        <v>4700</v>
       </c>
       <c r="G7" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="H7">
-        <v>55578388953</v>
+        <v>89588294768</v>
       </c>
       <c r="I7">
         <v>2</v>
       </c>
       <c r="L7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N7" t="s">
-        <v>136</v>
-      </c>
-      <c r="O7" t="s">
-        <v>137</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.4">
@@ -1603,37 +1570,37 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="C8" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D8" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="E8">
-        <v>19960</v>
+        <v>35020</v>
       </c>
       <c r="G8" t="s">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="H8">
-        <v>55578379444</v>
+        <v>89588294276</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="L8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N8" t="s">
-        <v>136</v>
+        <v>25</v>
       </c>
       <c r="O8" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
@@ -1641,37 +1608,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="C9" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="D9" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="E9">
-        <v>19960</v>
+        <v>8150</v>
       </c>
       <c r="G9" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="H9">
-        <v>55578340707</v>
+        <v>89588292691</v>
       </c>
       <c r="I9">
         <v>2</v>
       </c>
       <c r="L9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N9" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="O9" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.4">
@@ -1679,37 +1646,40 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="C10" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="E10">
-        <v>19010</v>
+        <v>14270</v>
       </c>
       <c r="G10" t="s">
-        <v>96</v>
+        <v>151</v>
       </c>
       <c r="H10">
-        <v>55578326006</v>
+        <v>89588291993</v>
       </c>
       <c r="I10">
         <v>2</v>
       </c>
+      <c r="J10" t="s">
+        <v>152</v>
+      </c>
       <c r="L10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N10" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="O10" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.4">
@@ -1717,37 +1687,40 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="C11" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D11" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E11">
-        <v>6800</v>
+        <v>14970</v>
       </c>
       <c r="G11" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="H11">
-        <v>89587633120</v>
+        <v>89588291938</v>
       </c>
       <c r="I11">
         <v>2</v>
       </c>
+      <c r="J11" t="s">
+        <v>158</v>
+      </c>
       <c r="L11" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" t="s">
+        <v>19</v>
+      </c>
+      <c r="N11" t="s">
         <v>20</v>
       </c>
-      <c r="M11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N11" t="s">
-        <v>136</v>
-      </c>
       <c r="O11" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.4">
@@ -1755,37 +1728,37 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C12" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D12" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E12">
-        <v>4160</v>
+        <v>24740</v>
       </c>
       <c r="G12" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H12">
-        <v>89587611854</v>
+        <v>89588291804</v>
       </c>
       <c r="I12">
         <v>2</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N12" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="O12" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.4">
@@ -1793,40 +1766,34 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C13" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D13" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E13">
-        <v>12750</v>
+        <v>6620</v>
       </c>
       <c r="G13" t="s">
-        <v>176</v>
+        <v>117</v>
       </c>
       <c r="H13">
-        <v>89587590454</v>
+        <v>89588291609</v>
       </c>
       <c r="I13">
         <v>2</v>
       </c>
-      <c r="K13" t="s">
-        <v>146</v>
-      </c>
       <c r="L13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N13" t="s">
-        <v>136</v>
-      </c>
-      <c r="O13" t="s">
-        <v>137</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.4">
@@ -1834,40 +1801,37 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C14" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D14" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E14">
-        <v>12750</v>
+        <v>64120</v>
       </c>
       <c r="G14" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H14">
-        <v>89587589992</v>
+        <v>89588291461</v>
       </c>
       <c r="I14">
         <v>2</v>
       </c>
-      <c r="K14" t="s">
-        <v>146</v>
-      </c>
       <c r="L14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N14" t="s">
-        <v>136</v>
+        <v>25</v>
       </c>
       <c r="O14" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.4">
@@ -1875,40 +1839,37 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C15" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D15" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E15">
-        <v>12750</v>
+        <v>20660</v>
       </c>
       <c r="G15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H15">
-        <v>89587590217</v>
+        <v>89588289698</v>
       </c>
       <c r="I15">
         <v>2</v>
       </c>
-      <c r="K15" t="s">
-        <v>146</v>
-      </c>
       <c r="L15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N15" t="s">
-        <v>136</v>
+        <v>42</v>
       </c>
       <c r="O15" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.4">
@@ -1916,40 +1877,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>179</v>
+      </c>
+      <c r="C16" t="s">
+        <v>180</v>
+      </c>
+      <c r="D16" t="s">
+        <v>181</v>
+      </c>
+      <c r="E16">
+        <v>8900</v>
+      </c>
+      <c r="G16" t="s">
+        <v>182</v>
+      </c>
+      <c r="H16">
+        <v>89588289104</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="K16" t="s">
         <v>183</v>
       </c>
-      <c r="C16" t="s">
-        <v>184</v>
-      </c>
-      <c r="D16" t="s">
-        <v>185</v>
-      </c>
-      <c r="E16">
-        <v>12750</v>
-      </c>
-      <c r="G16" t="s">
-        <v>176</v>
-      </c>
-      <c r="H16">
-        <v>89587589787</v>
-      </c>
-      <c r="I16">
-        <v>2</v>
-      </c>
-      <c r="K16" t="s">
-        <v>146</v>
-      </c>
       <c r="L16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N16" t="s">
-        <v>136</v>
-      </c>
-      <c r="O16" t="s">
-        <v>137</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.4">
@@ -1957,37 +1915,37 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>184</v>
+      </c>
+      <c r="C17" t="s">
+        <v>185</v>
+      </c>
+      <c r="D17" t="s">
         <v>186</v>
       </c>
-      <c r="C17" t="s">
-        <v>187</v>
-      </c>
-      <c r="D17" t="s">
-        <v>188</v>
-      </c>
       <c r="E17">
-        <v>13350</v>
+        <v>20800</v>
       </c>
       <c r="G17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="H17">
-        <v>89587504699</v>
+        <v>89588288833</v>
       </c>
       <c r="I17">
         <v>2</v>
       </c>
+      <c r="K17" t="s">
+        <v>183</v>
+      </c>
       <c r="L17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N17" t="s">
-        <v>136</v>
-      </c>
-      <c r="O17" t="s">
-        <v>137</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.4">
@@ -1995,43 +1953,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C18" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D18" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E18">
-        <v>10710</v>
+        <v>13500</v>
       </c>
       <c r="G18" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="H18">
-        <v>89587469700</v>
+        <v>89588288903</v>
       </c>
       <c r="I18">
         <v>2</v>
       </c>
-      <c r="J18" t="s">
-        <v>194</v>
-      </c>
       <c r="K18" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="L18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N18" t="s">
-        <v>195</v>
-      </c>
-      <c r="O18" t="s">
-        <v>196</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.4">
@@ -2039,43 +1991,37 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C19" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D19" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E19">
-        <v>10710</v>
+        <v>12900</v>
       </c>
       <c r="G19" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="H19">
-        <v>89587469464</v>
+        <v>89588288348</v>
       </c>
       <c r="I19">
         <v>2</v>
       </c>
-      <c r="J19" t="s">
-        <v>194</v>
-      </c>
       <c r="K19" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="L19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N19" t="s">
-        <v>195</v>
-      </c>
-      <c r="O19" t="s">
-        <v>200</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.4">
@@ -2083,87 +2029,37 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C20" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D20" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E20">
-        <v>10710</v>
+        <v>17280</v>
       </c>
       <c r="G20" t="s">
-        <v>193</v>
+        <v>117</v>
       </c>
       <c r="H20">
-        <v>89587468864</v>
+        <v>89588095858</v>
       </c>
       <c r="I20">
         <v>2</v>
       </c>
-      <c r="J20" t="s">
-        <v>194</v>
-      </c>
-      <c r="K20" t="s">
-        <v>146</v>
-      </c>
       <c r="L20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N20" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O20" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>204</v>
-      </c>
-      <c r="C21" t="s">
-        <v>205</v>
-      </c>
-      <c r="D21" t="s">
-        <v>206</v>
-      </c>
-      <c r="E21">
-        <v>7200</v>
-      </c>
-      <c r="G21" t="s">
-        <v>207</v>
-      </c>
-      <c r="H21">
-        <v>89587409201</v>
-      </c>
-      <c r="I21">
-        <v>2</v>
-      </c>
-      <c r="J21" t="s">
-        <v>194</v>
-      </c>
-      <c r="K21" t="s">
-        <v>146</v>
-      </c>
-      <c r="L21" t="s">
-        <v>20</v>
-      </c>
-      <c r="M21" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" t="s">
-        <v>195</v>
-      </c>
-      <c r="O21" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2173,7 +2069,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FD1B9B7-CABE-4891-9949-9276C745F61B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ED7600E-EEAE-4D33-B828-5416CA01EFAA}">
   <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -2229,37 +2125,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E2">
-        <v>23920</v>
+        <v>6810</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="H2">
-        <v>53858743882</v>
+        <v>89587612432</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N2" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
@@ -2267,37 +2163,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3">
+        <v>34200</v>
+      </c>
+      <c r="G3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3">
+        <v>89587761595</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O3" t="s">
         <v>43</v>
-      </c>
-      <c r="C3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3">
-        <v>17020</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3">
-        <v>53858734010</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="L3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N3" t="s">
-        <v>47</v>
-      </c>
-      <c r="O3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.4">
@@ -2305,37 +2201,43 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
         <v>49</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>50</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4">
+        <v>16770</v>
+      </c>
+      <c r="G4" t="s">
         <v>51</v>
       </c>
-      <c r="E4">
-        <v>57890</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
       <c r="H4">
-        <v>53858727893</v>
+        <v>89587718186</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
+      <c r="J4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" t="s">
+        <v>52</v>
+      </c>
       <c r="L4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" t="s">
         <v>20</v>
       </c>
-      <c r="M4" t="s">
-        <v>52</v>
-      </c>
-      <c r="N4" t="s">
-        <v>53</v>
-      </c>
       <c r="O4" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.4">
@@ -2343,37 +2245,37 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" t="s">
         <v>55</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5">
+        <v>15920</v>
+      </c>
+      <c r="G5" t="s">
         <v>56</v>
       </c>
-      <c r="D5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5">
-        <v>2970</v>
-      </c>
-      <c r="G5" t="s">
-        <v>58</v>
-      </c>
       <c r="H5">
-        <v>53858722011</v>
+        <v>89587706788</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="L5" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M5" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="N5" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="O5" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.4">
@@ -2381,37 +2283,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E6">
-        <v>28130</v>
+        <v>13360</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="H6">
-        <v>53858696356</v>
+        <v>89587681417</v>
       </c>
       <c r="I6">
         <v>2</v>
       </c>
       <c r="L6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="N6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="O6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.4">
@@ -2419,43 +2321,37 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="E7">
-        <v>31400</v>
+        <v>56080</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H7">
-        <v>89200019767</v>
+        <v>55578388953</v>
       </c>
       <c r="I7">
         <v>2</v>
       </c>
-      <c r="J7" t="s">
-        <v>34</v>
-      </c>
-      <c r="K7" t="s">
-        <v>34</v>
-      </c>
       <c r="L7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N7" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="O7" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.4">
@@ -2463,34 +2359,37 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="E8">
-        <v>49300</v>
+        <v>19960</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="H8">
-        <v>89199968681</v>
+        <v>55578379444</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="L8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N8" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="O8" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
@@ -2498,37 +2397,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9">
+        <v>19960</v>
+      </c>
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9">
+        <v>55578340707</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="L9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" t="s">
+        <v>19</v>
+      </c>
+      <c r="N9" t="s">
         <v>42</v>
       </c>
-      <c r="E9">
-        <v>47500</v>
-      </c>
-      <c r="G9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9">
-        <v>53858651732</v>
-      </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
-      <c r="L9" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" t="s">
-        <v>21</v>
-      </c>
-      <c r="N9" t="s">
-        <v>22</v>
-      </c>
       <c r="O9" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.4">
@@ -2536,37 +2435,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E10">
-        <v>17000</v>
+        <v>19010</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H10">
-        <v>53858622401</v>
+        <v>55578326006</v>
       </c>
       <c r="I10">
         <v>2</v>
       </c>
       <c r="L10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M10" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N10" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="O10" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.4">
@@ -2574,37 +2473,37 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E11">
-        <v>20430</v>
+        <v>6800</v>
       </c>
       <c r="G11" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="H11">
-        <v>89199897770</v>
+        <v>89587633120</v>
       </c>
       <c r="I11">
         <v>2</v>
       </c>
       <c r="L11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N11" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="O11" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.4">
@@ -2612,37 +2511,37 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E12">
-        <v>19300</v>
+        <v>4160</v>
       </c>
       <c r="G12" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="H12">
-        <v>89199841858</v>
+        <v>89587611854</v>
       </c>
       <c r="I12">
         <v>2</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N12" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="O12" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.4">
@@ -2659,28 +2558,31 @@
         <v>81</v>
       </c>
       <c r="E13">
-        <v>11400</v>
+        <v>12750</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="H13">
-        <v>53858521678</v>
+        <v>89587590454</v>
       </c>
       <c r="I13">
         <v>2</v>
       </c>
+      <c r="K13" t="s">
+        <v>52</v>
+      </c>
       <c r="L13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M13" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N13" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="O13" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.4">
@@ -2697,28 +2599,31 @@
         <v>85</v>
       </c>
       <c r="E14">
-        <v>79990</v>
+        <v>12750</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="H14">
-        <v>53858391642</v>
+        <v>89587589992</v>
       </c>
       <c r="I14">
         <v>2</v>
       </c>
+      <c r="K14" t="s">
+        <v>52</v>
+      </c>
       <c r="L14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N14" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="O14" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.4">
@@ -2735,31 +2640,31 @@
         <v>88</v>
       </c>
       <c r="E15">
-        <v>28340</v>
+        <v>12750</v>
       </c>
       <c r="G15" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="H15">
-        <v>53858387095</v>
+        <v>89587590217</v>
       </c>
       <c r="I15">
         <v>2</v>
       </c>
       <c r="K15" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="L15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N15" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="O15" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.4">
@@ -2767,37 +2672,40 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
         <v>90</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>91</v>
       </c>
-      <c r="D16" t="s">
-        <v>92</v>
-      </c>
       <c r="E16">
-        <v>42670</v>
+        <v>12750</v>
       </c>
       <c r="G16" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="H16">
-        <v>53858324859</v>
+        <v>89587589787</v>
       </c>
       <c r="I16">
         <v>2</v>
       </c>
+      <c r="K16" t="s">
+        <v>52</v>
+      </c>
       <c r="L16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M16" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N16" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="O16" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.4">
@@ -2805,37 +2713,37 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" t="s">
         <v>93</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>94</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17">
+        <v>13350</v>
+      </c>
+      <c r="G17" t="s">
         <v>95</v>
       </c>
-      <c r="E17">
-        <v>33870</v>
-      </c>
-      <c r="G17" t="s">
-        <v>96</v>
-      </c>
       <c r="H17">
-        <v>53858287681</v>
+        <v>89587504699</v>
       </c>
       <c r="I17">
         <v>2</v>
       </c>
       <c r="L17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M17" t="s">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="N17" t="s">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="O17" t="s">
-        <v>99</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.4">
@@ -2843,37 +2751,43 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18">
+        <v>10710</v>
+      </c>
+      <c r="G18" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18">
+        <v>89587469700</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18" t="s">
         <v>100</v>
       </c>
-      <c r="C18" t="s">
+      <c r="K18" t="s">
+        <v>52</v>
+      </c>
+      <c r="L18" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18" t="s">
+        <v>19</v>
+      </c>
+      <c r="N18" t="s">
         <v>101</v>
       </c>
-      <c r="D18" t="s">
+      <c r="O18" t="s">
         <v>102</v>
-      </c>
-      <c r="E18">
-        <v>38029</v>
-      </c>
-      <c r="G18" t="s">
-        <v>58</v>
-      </c>
-      <c r="H18">
-        <v>53858277897</v>
-      </c>
-      <c r="I18">
-        <v>2</v>
-      </c>
-      <c r="L18" t="s">
-        <v>20</v>
-      </c>
-      <c r="M18" t="s">
-        <v>21</v>
-      </c>
-      <c r="N18" t="s">
-        <v>103</v>
-      </c>
-      <c r="O18" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.4">
@@ -2881,37 +2795,43 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
         <v>105</v>
       </c>
-      <c r="C19" t="s">
+      <c r="E19">
+        <v>10710</v>
+      </c>
+      <c r="G19" t="s">
+        <v>99</v>
+      </c>
+      <c r="H19">
+        <v>89587469464</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19" t="s">
+        <v>100</v>
+      </c>
+      <c r="K19" t="s">
+        <v>52</v>
+      </c>
+      <c r="L19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M19" t="s">
+        <v>19</v>
+      </c>
+      <c r="N19" t="s">
+        <v>101</v>
+      </c>
+      <c r="O19" t="s">
         <v>106</v>
-      </c>
-      <c r="D19" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19">
-        <v>11100</v>
-      </c>
-      <c r="G19" t="s">
-        <v>96</v>
-      </c>
-      <c r="H19">
-        <v>53858271216</v>
-      </c>
-      <c r="I19">
-        <v>2</v>
-      </c>
-      <c r="L19" t="s">
-        <v>59</v>
-      </c>
-      <c r="M19" t="s">
-        <v>60</v>
-      </c>
-      <c r="N19" t="s">
-        <v>108</v>
-      </c>
-      <c r="O19" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.4">
@@ -2919,37 +2839,43 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E20">
-        <v>17150</v>
+        <v>10710</v>
       </c>
       <c r="G20" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="H20">
-        <v>89199782272</v>
+        <v>89587468864</v>
       </c>
       <c r="I20">
         <v>2</v>
       </c>
+      <c r="J20" t="s">
+        <v>100</v>
+      </c>
+      <c r="K20" t="s">
+        <v>52</v>
+      </c>
       <c r="L20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N20" t="s">
-        <v>22</v>
+        <v>101</v>
       </c>
       <c r="O20" t="s">
-        <v>23</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.4">
@@ -2957,37 +2883,43 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E21">
-        <v>30010</v>
+        <v>7200</v>
       </c>
       <c r="G21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H21">
-        <v>89199782212</v>
+        <v>89587409201</v>
       </c>
       <c r="I21">
         <v>2</v>
       </c>
+      <c r="J21" t="s">
+        <v>100</v>
+      </c>
+      <c r="K21" t="s">
+        <v>52</v>
+      </c>
       <c r="L21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M21" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="N21" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="O21" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/source/09_GenerativeAI_RPA/genai_rpa.xlsx
+++ b/source/09_GenerativeAI_RPA/genai_rpa.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai_x\source\09_GenerativeAI_RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF975919-C5EF-4145-987F-01D3FA180644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6AE8AC1-608C-4D92-9423-4882153260D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="origin_report" sheetId="26" r:id="rId1"/>
-    <sheet name="prev_report" sheetId="202" r:id="rId2"/>
-    <sheet name="now_report" sheetId="205" r:id="rId3"/>
+    <sheet name="now_report" sheetId="205" r:id="rId2"/>
+    <sheet name="prev_report" sheetId="210" r:id="rId3"/>
     <sheet name="now_report_en" sheetId="206" r:id="rId4"/>
     <sheet name="now_list" sheetId="204" r:id="rId5"/>
-    <sheet name="prev_list" sheetId="208" r:id="rId6"/>
+    <sheet name="prev_list" sheetId="209" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="212">
   <si>
     <t>OOO 일일 동향 보고서</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -98,35 +98,13 @@
     <t>미용/목욕</t>
   </si>
   <si>
-    <t>샴푸/린스/비누</t>
-  </si>
-  <si>
     <t>기타반려동물용품</t>
   </si>
   <si>
     <t>강아지 배변용품</t>
   </si>
   <si>
-    <t>11번가</t>
-  </si>
-  <si>
     <t>리빙용품</t>
-  </si>
-  <si>
-    <t>2025-03-30 15:56:04 기준</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prev_list와 now_list의 비교를 통해 다음과 같은 주요 특징을 도출할 수 있습니다.
-우선, 'image' 항목에 있는 이미지 URL이 prev_list와 now_list에서 차이가 있습니다. 예를 들어, 1위 상품 '개 대 정장 샴푸 프레스 대비누대 비누 블랙 치솔 칫솔 세트'의 이미지 URL이 prev_list에서는 'https://shopping-phinf.pstatic.net/main_5385874/53858743882.jpg'인 반면 now_list에서는 'https://shopping-phinf.pstatic.net/main_5385874/53858743882.jpg'으로 변경되지 않았습니다. 이는 이미지 품질이나 저장 경로의 안정성을 의미할 수 있습니다.
-가격 측면에서는 두 목록 모두 동일한 가격 정보를 제공하며, 특히 1위 상품은 23920원이 유지되고 있습니다. 쇼핑몰 정보는 또한 변동이 없으며, 1위부터 20위까지의 상품은 모두 '옥션', '쿠팡', 'TEMU kr', '11번가'와 같은 사이트에서 판매되고 있습니다.
-특히 다수의 상품이 '생활/건강' 카테고리 내에서 '반려동물' 관련 제품으로 분류되어 있으며, 20위까지의 상품 중 반려동물 관련 제품이 과반수 이상을 차지하고 있습니다. 이는 소비자들이 반려동물 제품에 대한 수요가 높아졌음을 반영합니다.
-결론적으로, prev_list와 now_list 간에는 큰 변화는 없지만 몇 가지 항목의 안정성과 반복된 반려동물 관련 제품의 출현이 눈에 띄며, 이는 현재 소비 트렌드와 관련이 깊다고 판단됩니다.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**올가홀푸드, 헬시 스낵 시장 진출**
-2025년 3월 21일, 올가홀푸드가 국내산 원물을 활용한 헬시 스낵 시장에 도전한다고 발표했다. 올가홀푸드는 건강을 중시하는 소비자 트렌드에 맞춰 고영양가 제품을 출시할 계획이다. 이를 통해 시장 점유율 확대를 목표로 하며, 특히 자연 재료와 무첨가 제품에 집중할 예정이다. 올가홀푸드는 독자적인 제조 공정을 통해 품질과 맛을 동시에 잡겠다는 전략을 세우고 있으며, 소비자들에게 직접 체험할 기회를 제공하는 이벤트도 계획 중이다. 이와 같은 혁신적인 접근은 헬시 스낵 분야의 경쟁을 더욱 치열하게 할 것으로 예상된다.
-</t>
   </si>
   <si>
     <t>OO Daily Insights</t>
@@ -172,234 +150,18 @@
 </t>
   </si>
   <si>
-    <t>75g 덴티 &lt;b&gt;포켄스&lt;/b&gt; 페어리 L D18 IWFI7HAK</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043101733</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958761/89587612432.jpg</t>
-  </si>
-  <si>
-    <t>도매도매24</t>
-  </si>
-  <si>
     <t>강아지 간식</t>
   </si>
   <si>
-    <t>개껌</t>
-  </si>
-  <si>
-    <t>입냄새감소 치석 애견껌 카누들 &lt;b&gt;포켄스&lt;/b&gt; 플러스S 60p CWF88C98</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043250896</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958776/89587761595.jpg</t>
-  </si>
-  <si>
-    <t>로얄하이츠</t>
-  </si>
-  <si>
-    <t>포비스 3in1 샴푸n린스 1000ml</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043207487</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958771/89587718186.jpg</t>
-  </si>
-  <si>
-    <t>gulink</t>
-  </si>
-  <si>
-    <t>포켄스</t>
-  </si>
-  <si>
-    <t>간식 후레시 강아지 칼슘 큰별 220g &lt;b&gt;포켄스&lt;/b&gt; 덴탈스틱</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043196089</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958770/89587706788.jpg</t>
-  </si>
-  <si>
-    <t>에코플렉스s</t>
-  </si>
-  <si>
-    <t>블루베리 큰별 후레시 &lt;b&gt;포켄스&lt;/b&gt; 220g 개껌 D18 덴탈스틱 NWFI7HA5</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043170721</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958768/89587681417.jpg</t>
-  </si>
-  <si>
-    <t>거성에테르</t>
-  </si>
-  <si>
-    <t>EXTREMO 우리 애기 &lt;b&gt;FORCANS&lt;/b&gt; 과일먹은 치즈덴탈껌 100g 9개세트</t>
-  </si>
-  <si>
-    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=7186993419&amp;tid=1000000061</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5557838/55578388953.jpg</t>
-  </si>
-  <si>
-    <t>EXTREMO 우리 애기 &lt;b&gt;FORCANS&lt;/b&gt; DENTAL STICK 오메가3 M 큰별 220g</t>
-  </si>
-  <si>
-    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=7186993417&amp;tid=1000000061</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5557837/55578379444.jpg</t>
-  </si>
-  <si>
-    <t>EXTREMO 우리 애기 &lt;b&gt;FORCANS&lt;/b&gt; DENTAL STICK 블루베리 M 220g</t>
-  </si>
-  <si>
-    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=7186993409&amp;tid=1000000061</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5557834/55578340707.jpg</t>
-  </si>
-  <si>
-    <t>EXTREMO 우리 애기 &lt;b&gt;FORCANS&lt;/b&gt; DENTAL STICK 블루베리 S 220g</t>
-  </si>
-  <si>
-    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=7186993414&amp;tid=1000000061</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5557832/55578326006.jpg</t>
-  </si>
-  <si>
-    <t>65g &lt;b&gt;포켄스&lt;/b&gt; D18 SS 덴티 페어리 OWFI7HAP</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043122423</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958763/89587633120.jpg</t>
-  </si>
-  <si>
-    <t>애견 개껌 반려견 100g 사과 &lt;b&gt;포켄스&lt;/b&gt; 간식 치즈덴탈껌 EW485B12</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043101155</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958761/89587611854.jpg</t>
-  </si>
-  <si>
-    <t>(M) 간식) (강아지 덴티 &lt;b&gt;포켄스&lt;/b&gt; 페어리 75g</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043079755</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958759/89587590454.jpg</t>
-  </si>
-  <si>
-    <t>윤댕쁘띠</t>
-  </si>
-  <si>
-    <t>덴티 &lt;b&gt;포켄스&lt;/b&gt; 간식) (강아지 65g (SS) 페어리</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043079293</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958758/89587589992.jpg</t>
-  </si>
-  <si>
-    <t>(L) &lt;b&gt;포켄스&lt;/b&gt; 75g 간식) (강아지 페어리 덴티</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043079518</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958759/89587590217.jpg</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;포켄스&lt;/b&gt; 덴티 간식) 페어리 (S) 65g (강아지</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043079088</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958758/89587589787.jpg</t>
-  </si>
-  <si>
-    <t>후레시 220g 개껌 D18 칼슘 &lt;b&gt;포켄스&lt;/b&gt; 큰별 덴탈스틱 PWFI7H9Y</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12042994000</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958750/89587504699.jpg</t>
-  </si>
-  <si>
-    <t>하니스토어20</t>
-  </si>
-  <si>
-    <t>냄새 감염방지 강아지 귀 청소 세정제 건강관리용품 포메귀</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12042959001</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958746/89587469700.jpg</t>
-  </si>
-  <si>
-    <t>무배의민족</t>
-  </si>
-  <si>
-    <t>더키코</t>
-  </si>
-  <si>
     <t>강아지 건강/관리용품</t>
   </si>
   <si>
     <t>눈/귀 관리용품</t>
   </si>
   <si>
-    <t>입냄새제거 이빨 잇몸 위생 애견 입 스프레이 뿌리는치약 여행</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12042958765</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958746/89587469464.jpg</t>
-  </si>
-  <si>
     <t>구강청결제</t>
   </si>
   <si>
-    <t>달콤한 딸기향 치석제거 강아지 먹는 치약 입냄새감소 위생용품</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12042958165</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958746/89587468864.jpg</t>
-  </si>
-  <si>
-    <t>입냄새제거 이빨 잇몸 위생 애견 입 스프레이 간편함 포메구강</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12042898502</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958740/89587409201.jpg</t>
-  </si>
-  <si>
-    <t>라이크미리빙</t>
-  </si>
-  <si>
     <t>그물망이 부드러운 대형뜰채</t>
   </si>
   <si>
@@ -650,6 +412,286 @@
   </si>
   <si>
     <t>분변통/모래삽</t>
+  </si>
+  <si>
+    <t>서락 쥬쥬베 실리콘 그물망 토일렛 SET 그린 배변&lt;b&gt;용품&lt;/b&gt; 배변 실리콘그물망화장실</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043893622</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958840/89588404320.jpg</t>
+  </si>
+  <si>
+    <t>모두의 서락</t>
+  </si>
+  <si>
+    <t>바이탈밀 후르츠맛 50g - 도마뱀 사료,크레 먹이,파충류 슈퍼푸드 (크레스티드게코,가고일게코,리키에너스)</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043926494</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958843/89588437193.jpg</t>
+  </si>
+  <si>
+    <t>도마뱀용품점</t>
+  </si>
+  <si>
+    <t>쥬쥬베 배변봉투 리필 90매 (랜덤발송)</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043803407</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958831/89588314106.jpg</t>
+  </si>
+  <si>
+    <t>위버스코리아</t>
+  </si>
+  <si>
+    <t>배변봉투/집게</t>
+  </si>
+  <si>
+    <t>서락 티티펫 파스텔 컬러 고양이 삽 파스텔삽</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043925398</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958843/89588436097.jpg</t>
+  </si>
+  <si>
+    <t>칫솔 인기 애견</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043925056</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958843/89588435755.jpg</t>
+  </si>
+  <si>
+    <t>여누세마켓</t>
+  </si>
+  <si>
+    <t>아트박스 팝아트 핸드크림 피치젤리</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043794453</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958830/89588305151.jpg</t>
+  </si>
+  <si>
+    <t>배변패드</t>
+  </si>
+  <si>
+    <t>강아지 미세먼지 마스크 3개입 애견 반려견 3중 필터 스트랩 마스크 중형</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043922472</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958843/89588433170.jpg</t>
+  </si>
+  <si>
+    <t>아랑존디</t>
+  </si>
+  <si>
+    <t>바이온</t>
+  </si>
+  <si>
+    <t>서락 시저 쇠고기 100g 24개 강아지간식 &lt;b&gt;애완&lt;/b&gt;동물용 애견&lt;b&gt;용품&lt;/b&gt; 강아지육포간식</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043922727</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958843/89588433426.jpg</t>
+  </si>
+  <si>
+    <t>캔/파우치</t>
+  </si>
+  <si>
+    <t>창 풍경 스티커 장식 정크 저널 콜라주 편지지 &lt;b&gt;애완&lt;/b&gt; 동물 스크랩북 1. A</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043791412</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958830/89588302111.jpg</t>
+  </si>
+  <si>
+    <t>가온라온12호점</t>
+  </si>
+  <si>
+    <t>문구/사무용품</t>
+  </si>
+  <si>
+    <t>스티커/테이프</t>
+  </si>
+  <si>
+    <t>스티커</t>
+  </si>
+  <si>
+    <t>투명 옷걸이 진열대 반려동물 걸이 진주니켈</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043921955</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958843/89588432654.jpg</t>
+  </si>
+  <si>
+    <t>아크아크샵</t>
+  </si>
+  <si>
+    <t>바이탈밀 인섹트맛 80g - 도마뱀 사료,크레 먹이,파충류 슈퍼푸드 (크레스티드게코,가고일게코,리키에너스)</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043920862</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958843/89588431561.jpg</t>
+  </si>
+  <si>
+    <t>[HN2] 반려동물 탈취제 냄새제거 은나노탈취제 라벤더향</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043920581</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958843/89588431280.jpg</t>
+  </si>
+  <si>
+    <t>해븐하트</t>
+  </si>
+  <si>
+    <t>펫앤드림</t>
+  </si>
+  <si>
+    <t>탈취제/소독제</t>
+  </si>
+  <si>
+    <t>보관 곤충 파충류 채집통 다슬기 관찰통 케이스 중 사슴벌레</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043878023</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958838/89588388722.jpg</t>
+  </si>
+  <si>
+    <t>딩거의추천샵</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;애완&lt;/b&gt;동물 쓰레기통으로 교체하는 4Pcs 활성탄 필터, 공기 필터용 6 x 인치 교체 냄새 필터</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043919911</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958843/89588430610.jpg</t>
+  </si>
+  <si>
+    <t>핫딜마켓샵</t>
+  </si>
+  <si>
+    <t>자동화장실</t>
+  </si>
+  <si>
+    <t>고양이와 개 &lt;b&gt;애완&lt;/b&gt; 동물 플러시 공룡 장난감 파괴 할 수없는 씹는 작은 큰 개를위한 삐걱 거리는 소리 &lt;b&gt;용품&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043918996</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958842/89588429695.jpg</t>
+  </si>
+  <si>
+    <t>보시</t>
+  </si>
+  <si>
+    <t>장난감/토이</t>
+  </si>
+  <si>
+    <t>프리미엄 창문 스크린 DIY 키트 39 x 51 비 &lt;b&gt;애완&lt;/b&gt;동물 긁힘 꽃가루 미세먼지 99 30메쉬 내구성 신소재 도구 포함 폭 길이 190 51in X 190in-KIT</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043918827</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958842/89588429526.jpg</t>
+  </si>
+  <si>
+    <t>비에치22번가</t>
+  </si>
+  <si>
+    <t>청소용품</t>
+  </si>
+  <si>
+    <t>기타청소용품</t>
+  </si>
+  <si>
+    <t>생분해 반려동물 배변봉투 강아지 고양이 산책 위생봉투 풉백</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043918461</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958842/89588429160.jpg</t>
+  </si>
+  <si>
+    <t>반려동물 위생 눈꼽빗 스테인리스 이물질 제거 강아지 고양이 겸용 애견&lt;b&gt;용품&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043918465</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958842/89588429164.jpg</t>
+  </si>
+  <si>
+    <t>브러시/빗</t>
+  </si>
+  <si>
+    <t>반려동물 배변봉투 풉백 디스펜서 휴대용 캡슐형 강아지 산책용</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043918462</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958842/89588429161.jpg</t>
+  </si>
+  <si>
+    <t>반려동물 손가락 칫솔 강아지 고양이 투명 실리콘 구강 위생 관리</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043918471</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958842/89588429167.jpg</t>
+  </si>
+  <si>
+    <t>고양이 건강/관리용품</t>
+  </si>
+  <si>
+    <t>구강관리용품</t>
+  </si>
+  <si>
+    <t>2025-07-01 16:28:30 기준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신상품 배변용품, 파충류 사료 등장하며 가격↑, 브랜드 및 카테고리도 변경됨.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 한국 기술과 생산품이 미국·중국, 러시아 등에서 인기, 2025년 1분기 생활 필수품 수요는 전년대비 2배 성장.  
+- 인천 반값택배 이용 소상공인 32.7%, 매출 증가 효과 확인.  
+- 반려동물 양육비는 월 19만원, 치료비는 2배 증가, 시장은 2022년~2024년 연평균 1.4% 성장.  
+- 애완용품 점포 수는 늘었지만 점당 매출은 감소, 시장은 연평균 1.4% 증가, 가맹점 4.2% 증가.  
+- 북한은 고급 와인, 명품시계, 애견용품 등 다양한 상품을 수입.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1136,55 +1178,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="85.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="36" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="384" x14ac:dyDescent="0.4">
-      <c r="A5" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="7" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" s="3" customFormat="1" ht="172.8" x14ac:dyDescent="0.4">
-      <c r="A8" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.5" right="0.42" top="0.75" bottom="0.28999999999999998" header="0.3" footer="0.44"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -1202,7 +1195,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
-        <v>30</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
@@ -1210,9 +1203,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="403.2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:1" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
-        <v>33</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -1221,9 +1214,58 @@
         <v>2</v>
       </c>
     </row>
+    <row r="8" spans="1:1" s="3" customFormat="1" ht="115.2" x14ac:dyDescent="0.4">
+      <c r="A8" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.5" right="0.42" top="0.75" bottom="0.28999999999999998" header="0.3" footer="0.44"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A216B37A-CDEF-4B8E-85BA-9DC942EA39C9}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="85.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="36" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="403.2" x14ac:dyDescent="0.4">
+      <c r="A5" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="7" spans="1:1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
     <row r="8" spans="1:1" s="3" customFormat="1" ht="172.8" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1246,33 +1288,33 @@
   <sheetData>
     <row r="1" spans="1:1" ht="36" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="384" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="7" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:1" s="3" customFormat="1" ht="230.4" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1284,7 +1326,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.4">
@@ -1339,22 +1381,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E2">
-        <v>4130</v>
+        <v>57480</v>
       </c>
       <c r="G2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="H2">
-        <v>89588297426</v>
+        <v>89588404320</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -1368,38 +1410,35 @@
       <c r="N2" t="s">
         <v>22</v>
       </c>
+      <c r="O2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E3">
-        <v>8230</v>
+        <v>15000</v>
       </c>
       <c r="G3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="H3">
-        <v>89588296203</v>
+        <v>89588437193</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
-      <c r="J3" t="s">
-        <v>121</v>
-      </c>
-      <c r="K3" t="s">
-        <v>121</v>
-      </c>
       <c r="L3" t="s">
         <v>18</v>
       </c>
@@ -1407,10 +1446,7 @@
         <v>19</v>
       </c>
       <c r="N3" t="s">
-        <v>101</v>
-      </c>
-      <c r="O3" t="s">
-        <v>102</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.4">
@@ -1418,28 +1454,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E4">
-        <v>13200</v>
+        <v>2130</v>
       </c>
       <c r="G4" t="s">
-        <v>117</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>89588296271</v>
+        <v>89588314106</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
-      <c r="J4" t="s">
-        <v>125</v>
+      <c r="K4" t="s">
+        <v>132</v>
       </c>
       <c r="L4" t="s">
         <v>18</v>
@@ -1448,10 +1484,10 @@
         <v>19</v>
       </c>
       <c r="N4" t="s">
-        <v>126</v>
+        <v>22</v>
       </c>
       <c r="O4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.4">
@@ -1459,22 +1495,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E5">
-        <v>282100</v>
+        <v>1880</v>
       </c>
       <c r="G5" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H5">
-        <v>89588295630</v>
+        <v>89588436097</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -1486,10 +1522,10 @@
         <v>19</v>
       </c>
       <c r="N5" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="O5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.4">
@@ -1497,22 +1533,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E6">
-        <v>16570</v>
+        <v>5780</v>
       </c>
       <c r="G6" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="H6">
-        <v>89588295040</v>
+        <v>89588435755</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -1524,10 +1560,10 @@
         <v>19</v>
       </c>
       <c r="N6" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O6" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.4">
@@ -1535,25 +1571,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E7">
-        <v>4700</v>
+        <v>2000</v>
       </c>
       <c r="G7" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="H7">
-        <v>89588294768</v>
+        <v>89588305151</v>
       </c>
       <c r="I7">
         <v>2</v>
+      </c>
+      <c r="K7" t="s">
+        <v>106</v>
       </c>
       <c r="L7" t="s">
         <v>18</v>
@@ -1563,6 +1602,9 @@
       </c>
       <c r="N7" t="s">
         <v>22</v>
+      </c>
+      <c r="O7" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.4">
@@ -1570,26 +1612,29 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C8" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E8">
-        <v>35020</v>
+        <v>8380</v>
       </c>
       <c r="G8" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H8">
-        <v>89588294276</v>
+        <v>89588433170</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
+      <c r="K8" t="s">
+        <v>149</v>
+      </c>
       <c r="L8" t="s">
         <v>18</v>
       </c>
@@ -1597,10 +1642,7 @@
         <v>19</v>
       </c>
       <c r="N8" t="s">
-        <v>25</v>
-      </c>
-      <c r="O8" t="s">
-        <v>143</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
@@ -1608,22 +1650,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="E9">
-        <v>8150</v>
+        <v>51900</v>
       </c>
       <c r="G9" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="H9">
-        <v>89588292691</v>
+        <v>89588433426</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -1635,10 +1677,10 @@
         <v>19</v>
       </c>
       <c r="N9" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="O9" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.4">
@@ -1646,40 +1688,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C10" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D10" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E10">
-        <v>14270</v>
+        <v>9900</v>
       </c>
       <c r="G10" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="H10">
-        <v>89588291993</v>
+        <v>89588302111</v>
       </c>
       <c r="I10">
         <v>2</v>
       </c>
-      <c r="J10" t="s">
-        <v>152</v>
-      </c>
       <c r="L10" t="s">
         <v>18</v>
       </c>
       <c r="M10" t="s">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="N10" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="O10" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.4">
@@ -1687,29 +1726,26 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C11" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D11" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E11">
-        <v>14970</v>
+        <v>76330</v>
       </c>
       <c r="G11" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="H11">
-        <v>89588291938</v>
+        <v>89588432654</v>
       </c>
       <c r="I11">
         <v>2</v>
       </c>
-      <c r="J11" t="s">
-        <v>158</v>
-      </c>
       <c r="L11" t="s">
         <v>18</v>
       </c>
@@ -1717,10 +1753,7 @@
         <v>19</v>
       </c>
       <c r="N11" t="s">
-        <v>20</v>
-      </c>
-      <c r="O11" t="s">
-        <v>159</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.4">
@@ -1728,22 +1761,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C12" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D12" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E12">
-        <v>24740</v>
+        <v>16000</v>
       </c>
       <c r="G12" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="H12">
-        <v>89588291804</v>
+        <v>89588431561</v>
       </c>
       <c r="I12">
         <v>2</v>
@@ -1755,10 +1788,7 @@
         <v>19</v>
       </c>
       <c r="N12" t="s">
-        <v>164</v>
-      </c>
-      <c r="O12" t="s">
-        <v>165</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.4">
@@ -1766,25 +1796,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D13" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E13">
-        <v>6620</v>
+        <v>16650</v>
       </c>
       <c r="G13" t="s">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="H13">
-        <v>89588291609</v>
+        <v>89588431280</v>
       </c>
       <c r="I13">
         <v>2</v>
+      </c>
+      <c r="K13" t="s">
+        <v>172</v>
       </c>
       <c r="L13" t="s">
         <v>18</v>
@@ -1794,6 +1827,9 @@
       </c>
       <c r="N13" t="s">
         <v>22</v>
+      </c>
+      <c r="O13" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.4">
@@ -1801,22 +1837,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C14" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D14" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E14">
-        <v>64120</v>
+        <v>5500</v>
       </c>
       <c r="G14" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H14">
-        <v>89588291461</v>
+        <v>89588388722</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -1828,10 +1864,7 @@
         <v>19</v>
       </c>
       <c r="N14" t="s">
-        <v>25</v>
-      </c>
-      <c r="O14" t="s">
-        <v>173</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.4">
@@ -1839,22 +1872,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C15" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D15" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E15">
-        <v>20660</v>
+        <v>60120</v>
       </c>
       <c r="G15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H15">
-        <v>89588289698</v>
+        <v>89588430610</v>
       </c>
       <c r="I15">
         <v>2</v>
@@ -1866,10 +1899,10 @@
         <v>19</v>
       </c>
       <c r="N15" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="O15" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.4">
@@ -1877,29 +1910,26 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C16" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D16" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E16">
-        <v>8900</v>
+        <v>11700</v>
       </c>
       <c r="G16" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H16">
-        <v>89588289104</v>
+        <v>89588429695</v>
       </c>
       <c r="I16">
         <v>2</v>
       </c>
-      <c r="K16" t="s">
-        <v>183</v>
-      </c>
       <c r="L16" t="s">
         <v>18</v>
       </c>
@@ -1907,7 +1937,10 @@
         <v>19</v>
       </c>
       <c r="N16" t="s">
-        <v>22</v>
+        <v>49</v>
+      </c>
+      <c r="O16" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.4">
@@ -1915,37 +1948,34 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C17" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E17">
-        <v>20800</v>
+        <v>237800</v>
       </c>
       <c r="G17" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H17">
-        <v>89588288833</v>
+        <v>89588429526</v>
       </c>
       <c r="I17">
         <v>2</v>
       </c>
-      <c r="K17" t="s">
-        <v>183</v>
-      </c>
       <c r="L17" t="s">
         <v>18</v>
       </c>
       <c r="M17" t="s">
-        <v>19</v>
+        <v>192</v>
       </c>
       <c r="N17" t="s">
-        <v>22</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.4">
@@ -1953,28 +1983,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C18" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D18" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E18">
-        <v>13500</v>
+        <v>1080</v>
       </c>
       <c r="G18" t="s">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="H18">
-        <v>89588288903</v>
+        <v>89588429160</v>
       </c>
       <c r="I18">
         <v>2</v>
-      </c>
-      <c r="K18" t="s">
-        <v>183</v>
       </c>
       <c r="L18" t="s">
         <v>18</v>
@@ -1985,35 +2012,35 @@
       <c r="N18" t="s">
         <v>22</v>
       </c>
+      <c r="O18" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C19" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="D19" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E19">
-        <v>12900</v>
+        <v>1570</v>
       </c>
       <c r="G19" t="s">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="H19">
-        <v>89588288348</v>
+        <v>89588429164</v>
       </c>
       <c r="I19">
         <v>2</v>
       </c>
-      <c r="K19" t="s">
-        <v>183</v>
-      </c>
       <c r="L19" t="s">
         <v>18</v>
       </c>
@@ -2021,7 +2048,10 @@
         <v>19</v>
       </c>
       <c r="N19" t="s">
-        <v>22</v>
+        <v>20</v>
+      </c>
+      <c r="O19" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.4">
@@ -2029,22 +2059,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C20" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="D20" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="E20">
-        <v>17280</v>
+        <v>1570</v>
       </c>
       <c r="G20" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="H20">
-        <v>89588095858</v>
+        <v>89588429161</v>
       </c>
       <c r="I20">
         <v>2</v>
@@ -2056,10 +2086,48 @@
         <v>19</v>
       </c>
       <c r="N20" t="s">
-        <v>196</v>
+        <v>22</v>
       </c>
       <c r="O20" t="s">
-        <v>197</v>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>204</v>
+      </c>
+      <c r="C21" t="s">
+        <v>205</v>
+      </c>
+      <c r="D21" t="s">
+        <v>206</v>
+      </c>
+      <c r="E21">
+        <v>890</v>
+      </c>
+      <c r="G21" t="s">
+        <v>148</v>
+      </c>
+      <c r="H21">
+        <v>89588429167</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
+      </c>
+      <c r="L21" t="s">
+        <v>18</v>
+      </c>
+      <c r="M21" t="s">
+        <v>19</v>
+      </c>
+      <c r="N21" t="s">
+        <v>207</v>
+      </c>
+      <c r="O21" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -2069,8 +2137,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ED7600E-EEAE-4D33-B828-5416CA01EFAA}">
-  <dimension ref="A1:O21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C28800-3831-467E-8CF5-53CC2ABF0E18}">
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.4">
@@ -2125,22 +2193,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
         <v>38</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>39</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2">
+        <v>4130</v>
+      </c>
+      <c r="G2" t="s">
         <v>40</v>
       </c>
-      <c r="E2">
-        <v>6810</v>
-      </c>
-      <c r="G2" t="s">
-        <v>41</v>
-      </c>
       <c r="H2">
-        <v>89587612432</v>
+        <v>89588297426</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -2152,10 +2220,7 @@
         <v>19</v>
       </c>
       <c r="N2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
@@ -2163,25 +2228,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3">
+        <v>8230</v>
+      </c>
+      <c r="G3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3">
+        <v>89588296203</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3" t="s">
         <v>44</v>
       </c>
-      <c r="C3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3">
-        <v>34200</v>
-      </c>
-      <c r="G3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3">
-        <v>89587761595</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
+      <c r="K3" t="s">
+        <v>44</v>
       </c>
       <c r="L3" t="s">
         <v>18</v>
@@ -2190,10 +2261,10 @@
         <v>19</v>
       </c>
       <c r="N3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="O3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.4">
@@ -2201,43 +2272,40 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4">
+        <v>13200</v>
+      </c>
+      <c r="G4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4">
+        <v>89588296271</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4" t="s">
         <v>48</v>
       </c>
-      <c r="C4" t="s">
+      <c r="L4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" t="s">
         <v>49</v>
       </c>
-      <c r="D4" t="s">
+      <c r="O4" t="s">
         <v>50</v>
-      </c>
-      <c r="E4">
-        <v>16770</v>
-      </c>
-      <c r="G4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H4">
-        <v>89587718186</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K4" t="s">
-        <v>52</v>
-      </c>
-      <c r="L4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M4" t="s">
-        <v>19</v>
-      </c>
-      <c r="N4" t="s">
-        <v>20</v>
-      </c>
-      <c r="O4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.4">
@@ -2245,22 +2313,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" t="s">
         <v>53</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5">
+        <v>282100</v>
+      </c>
+      <c r="G5" t="s">
         <v>54</v>
       </c>
-      <c r="D5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5">
-        <v>15920</v>
-      </c>
-      <c r="G5" t="s">
-        <v>56</v>
-      </c>
       <c r="H5">
-        <v>89587706788</v>
+        <v>89588295630</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -2272,10 +2340,10 @@
         <v>19</v>
       </c>
       <c r="N5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="O5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.4">
@@ -2283,37 +2351,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" t="s">
         <v>57</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6">
+        <v>16570</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6">
+        <v>89588295040</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="L6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" t="s">
+        <v>19</v>
+      </c>
+      <c r="N6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6" t="s">
         <v>58</v>
-      </c>
-      <c r="D6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6">
-        <v>13360</v>
-      </c>
-      <c r="G6" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6">
-        <v>89587681417</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="L6" t="s">
-        <v>18</v>
-      </c>
-      <c r="M6" t="s">
-        <v>19</v>
-      </c>
-      <c r="N6" t="s">
-        <v>42</v>
-      </c>
-      <c r="O6" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.4">
@@ -2321,22 +2389,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" t="s">
         <v>61</v>
       </c>
-      <c r="C7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" t="s">
-        <v>63</v>
-      </c>
       <c r="E7">
-        <v>56080</v>
+        <v>4700</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H7">
-        <v>55578388953</v>
+        <v>89588294768</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -2348,10 +2416,7 @@
         <v>19</v>
       </c>
       <c r="N7" t="s">
-        <v>42</v>
-      </c>
-      <c r="O7" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.4">
@@ -2359,37 +2424,37 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" t="s">
         <v>64</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8">
+        <v>35020</v>
+      </c>
+      <c r="G8" t="s">
         <v>65</v>
       </c>
-      <c r="D8" t="s">
+      <c r="H8">
+        <v>89588294276</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="L8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" t="s">
+        <v>19</v>
+      </c>
+      <c r="N8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" t="s">
         <v>66</v>
-      </c>
-      <c r="E8">
-        <v>19960</v>
-      </c>
-      <c r="G8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8">
-        <v>55578379444</v>
-      </c>
-      <c r="I8">
-        <v>2</v>
-      </c>
-      <c r="L8" t="s">
-        <v>18</v>
-      </c>
-      <c r="M8" t="s">
-        <v>19</v>
-      </c>
-      <c r="N8" t="s">
-        <v>42</v>
-      </c>
-      <c r="O8" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
@@ -2406,13 +2471,13 @@
         <v>69</v>
       </c>
       <c r="E9">
-        <v>19960</v>
+        <v>8150</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H9">
-        <v>55578340707</v>
+        <v>89588292691</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -2424,10 +2489,10 @@
         <v>19</v>
       </c>
       <c r="N9" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="O9" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.4">
@@ -2435,26 +2500,29 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E10">
-        <v>19010</v>
+        <v>14270</v>
       </c>
       <c r="G10" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="H10">
-        <v>55578326006</v>
+        <v>89588291993</v>
       </c>
       <c r="I10">
         <v>2</v>
       </c>
+      <c r="J10" t="s">
+        <v>75</v>
+      </c>
       <c r="L10" t="s">
         <v>18</v>
       </c>
@@ -2462,10 +2530,10 @@
         <v>19</v>
       </c>
       <c r="N10" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="O10" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.4">
@@ -2473,26 +2541,29 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E11">
-        <v>6800</v>
+        <v>14970</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H11">
-        <v>89587633120</v>
+        <v>89588291938</v>
       </c>
       <c r="I11">
         <v>2</v>
       </c>
+      <c r="J11" t="s">
+        <v>81</v>
+      </c>
       <c r="L11" t="s">
         <v>18</v>
       </c>
@@ -2500,10 +2571,10 @@
         <v>19</v>
       </c>
       <c r="N11" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="O11" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.4">
@@ -2511,22 +2582,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E12">
-        <v>4160</v>
+        <v>24740</v>
       </c>
       <c r="G12" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="H12">
-        <v>89587611854</v>
+        <v>89588291804</v>
       </c>
       <c r="I12">
         <v>2</v>
@@ -2538,10 +2609,10 @@
         <v>19</v>
       </c>
       <c r="N12" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="O12" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.4">
@@ -2549,29 +2620,26 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E13">
-        <v>12750</v>
+        <v>6620</v>
       </c>
       <c r="G13" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="H13">
-        <v>89587590454</v>
+        <v>89588291609</v>
       </c>
       <c r="I13">
         <v>2</v>
       </c>
-      <c r="K13" t="s">
-        <v>52</v>
-      </c>
       <c r="L13" t="s">
         <v>18</v>
       </c>
@@ -2579,10 +2647,7 @@
         <v>19</v>
       </c>
       <c r="N13" t="s">
-        <v>42</v>
-      </c>
-      <c r="O13" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.4">
@@ -2590,29 +2655,26 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E14">
-        <v>12750</v>
+        <v>64120</v>
       </c>
       <c r="G14" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H14">
-        <v>89587589992</v>
+        <v>89588291461</v>
       </c>
       <c r="I14">
         <v>2</v>
       </c>
-      <c r="K14" t="s">
-        <v>52</v>
-      </c>
       <c r="L14" t="s">
         <v>18</v>
       </c>
@@ -2620,10 +2682,10 @@
         <v>19</v>
       </c>
       <c r="N14" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="O14" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.4">
@@ -2631,29 +2693,26 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E15">
-        <v>12750</v>
+        <v>20660</v>
       </c>
       <c r="G15" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H15">
-        <v>89587590217</v>
+        <v>89588289698</v>
       </c>
       <c r="I15">
         <v>2</v>
       </c>
-      <c r="K15" t="s">
-        <v>52</v>
-      </c>
       <c r="L15" t="s">
         <v>18</v>
       </c>
@@ -2661,10 +2720,10 @@
         <v>19</v>
       </c>
       <c r="N15" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="O15" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.4">
@@ -2672,28 +2731,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E16">
-        <v>12750</v>
+        <v>8900</v>
       </c>
       <c r="G16" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="H16">
-        <v>89587589787</v>
+        <v>89588289104</v>
       </c>
       <c r="I16">
         <v>2</v>
       </c>
       <c r="K16" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="L16" t="s">
         <v>18</v>
@@ -2702,10 +2761,7 @@
         <v>19</v>
       </c>
       <c r="N16" t="s">
-        <v>42</v>
-      </c>
-      <c r="O16" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.4">
@@ -2713,26 +2769,29 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="E17">
-        <v>13350</v>
+        <v>20800</v>
       </c>
       <c r="G17" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H17">
-        <v>89587504699</v>
+        <v>89588288833</v>
       </c>
       <c r="I17">
         <v>2</v>
       </c>
+      <c r="K17" t="s">
+        <v>106</v>
+      </c>
       <c r="L17" t="s">
         <v>18</v>
       </c>
@@ -2740,10 +2799,7 @@
         <v>19</v>
       </c>
       <c r="N17" t="s">
-        <v>42</v>
-      </c>
-      <c r="O17" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.4">
@@ -2751,31 +2807,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="E18">
-        <v>10710</v>
+        <v>13500</v>
       </c>
       <c r="G18" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="H18">
-        <v>89587469700</v>
+        <v>89588288903</v>
       </c>
       <c r="I18">
         <v>2</v>
       </c>
-      <c r="J18" t="s">
-        <v>100</v>
-      </c>
       <c r="K18" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="L18" t="s">
         <v>18</v>
@@ -2784,10 +2837,7 @@
         <v>19</v>
       </c>
       <c r="N18" t="s">
-        <v>101</v>
-      </c>
-      <c r="O18" t="s">
-        <v>102</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.4">
@@ -2795,31 +2845,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19">
+        <v>12900</v>
+      </c>
+      <c r="G19" t="s">
         <v>105</v>
       </c>
-      <c r="E19">
-        <v>10710</v>
-      </c>
-      <c r="G19" t="s">
-        <v>99</v>
-      </c>
       <c r="H19">
-        <v>89587469464</v>
+        <v>89588288348</v>
       </c>
       <c r="I19">
         <v>2</v>
       </c>
-      <c r="J19" t="s">
-        <v>100</v>
-      </c>
       <c r="K19" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="L19" t="s">
         <v>18</v>
@@ -2828,10 +2875,7 @@
         <v>19</v>
       </c>
       <c r="N19" t="s">
-        <v>101</v>
-      </c>
-      <c r="O19" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.4">
@@ -2839,32 +2883,26 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D20" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="E20">
-        <v>10710</v>
+        <v>17280</v>
       </c>
       <c r="G20" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="H20">
-        <v>89587468864</v>
+        <v>89588095858</v>
       </c>
       <c r="I20">
         <v>2</v>
       </c>
-      <c r="J20" t="s">
-        <v>100</v>
-      </c>
-      <c r="K20" t="s">
-        <v>52</v>
-      </c>
       <c r="L20" t="s">
         <v>18</v>
       </c>
@@ -2872,54 +2910,10 @@
         <v>19</v>
       </c>
       <c r="N20" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="O20" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" t="s">
-        <v>112</v>
-      </c>
-      <c r="E21">
-        <v>7200</v>
-      </c>
-      <c r="G21" t="s">
-        <v>113</v>
-      </c>
-      <c r="H21">
-        <v>89587409201</v>
-      </c>
-      <c r="I21">
-        <v>2</v>
-      </c>
-      <c r="J21" t="s">
-        <v>100</v>
-      </c>
-      <c r="K21" t="s">
-        <v>52</v>
-      </c>
-      <c r="L21" t="s">
-        <v>18</v>
-      </c>
-      <c r="M21" t="s">
-        <v>19</v>
-      </c>
-      <c r="N21" t="s">
-        <v>101</v>
-      </c>
-      <c r="O21" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/source/09_GenerativeAI_RPA/genai_rpa.xlsx
+++ b/source/09_GenerativeAI_RPA/genai_rpa.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai_x\source\09_GenerativeAI_RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6AE8AC1-608C-4D92-9423-4882153260D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2422930-4635-40B2-ABA2-E56477744678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="origin_report" sheetId="26" r:id="rId1"/>
     <sheet name="now_report" sheetId="205" r:id="rId2"/>
-    <sheet name="prev_report" sheetId="210" r:id="rId3"/>
+    <sheet name="prev_report" sheetId="212" r:id="rId3"/>
     <sheet name="now_report_en" sheetId="206" r:id="rId4"/>
     <sheet name="now_list" sheetId="204" r:id="rId5"/>
-    <sheet name="prev_list" sheetId="209" r:id="rId6"/>
+    <sheet name="prev_list" sheetId="211" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="201">
   <si>
     <t>OOO 일일 동향 보고서</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -104,29 +104,15 @@
     <t>강아지 배변용품</t>
   </si>
   <si>
-    <t>리빙용품</t>
-  </si>
-  <si>
     <t>OO Daily Insights</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2025-03-30 15:56:46 기준</t>
-  </si>
-  <si>
     <t>2025-03-30 15:56:46</t>
   </si>
   <si>
     <t>- Open Market Search Result Updates</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">prev_list와 now_list 목록을 비교한 결과, 두 목록 간의 주요 특징 변화는 다음과 같습니다.
-첫째, 이미지 링크의 변화입니다. 예를 들어, '개 대 정장 샴푸 프레스 대비누대 비누 블랙 치솔 칫솔 세트'의 이미지가 prev_list에서는 "https://shopping-phinf.pstatic.net/main_5385874/53858743882.jpg"였으나, now_list에서는 이미지 경로가 동일하지만 파일명 숫자가 다릅니다. 이는 이미지 파일 업데이트를 나타낼 수 있습니다.
-둘째, 일부 제품의 가격이 변동했습니다. '바란스 개세정액 화이트워시 브라이트 백모용 503ml'는 prev_list에서 17150원이었고, now_list에서도 같은 가격이 유지되고 있지만, 다른 제품들은 변동이 있을 수 있습니다. 가격 변화가 있는 경우, 소비자에게 새로운 가격 정책이나 세일 정보를 제공할 가능성이 높습니다.
-셋째, 쇼핑몰 이름의 변화는 없으나, 특정 제품의 카테고리 정보에 대한 정리가 이루어진 것으로 확인됩니다. 예를 들어, '강아지발도장 동물 고양이 강아지 발자국 아크릴 스탬프'와 같은 아이템들은 이제 관련 카테고리가 더욱 명확하게 나열되었습니다.
-마지막으로, 일부 제품의 품명이 조금 더 간결하게 바뀌며 보다 깔끔한 정보를 제공하고 있습니다. 이를 통해 소비자는 더 손쉽게 제품을 이해하고 선택할 수 있을 것입니다. 전체적으로, now_list는 이미지 및 제품 정보 개선을 꾀했음을 알 수 있습니다.
-</t>
   </si>
   <si>
     <t xml:space="preserve">After comparing the previous and current lists, we can identify significant changes between the two. First, the image link for the first product has been updated from "https://shopping-phinf.pstatic.net/main_5385874/53858743882.jpg" to "https://shopping-phinf.pstatic.net/main_5385874/53858743882.jpg," indicating a minor change in the image. Additionally, the title and other details remain consistent across both lists.
@@ -140,11 +126,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">**올가홀푸드, 헬시 스낵 시장 도전**
-2025년 3월 21일, 올가홀푸드는 헬시 스낵 시장에 진출하겠다고 발표했다. 국내산 원물을 활용해 건강한 간식 옵션을 제공하며, 소비자들에게 더 나은 선택지를 제안하는 것이 목표다. 이 회사는 최근 증가하는 건강식품 소비 추세를 반영하여, 특히 면역력 강화를 중시하는 제품 라인을 선보일 예정이다. 올가홀푸드는 기존의 비타민 및 미용 관련 상품 외에, 저당 및 고단백 스낵도 추가하여 소비자 층을 확장할 계획이다. 이 initiative는 건강한 라이프스타일을 추구하는 현대인의 요구에 부응하려는 노력의 일환으로, 시장에서의 입지를 강화할 것으로 기대된다.
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">**Olga Whole Foods Enters Healthy Snack Market**
 On March 21, 2025, Olga Whole Foods announced its foray into the healthy snack market, focusing on domestic health products. With an increasing consumer demand for nutritious food options, Olga aims to leverage locally sourced ingredients to create a diverse range of snacks. This initiative aligns with the global trend of growing health consciousness, particularly among younger generations. The company plans to launch its first line of products by the end of April 2025, anticipating a significant response from health-oriented consumers. As competitors in the market intensify, Olga Whole Foods seeks to distinguish itself by emphasizing the quality and provenance of its ingredients, ensuring a strong position in this competitive segment.
 </t>
@@ -156,256 +137,22 @@
     <t>강아지 건강/관리용품</t>
   </si>
   <si>
-    <t>눈/귀 관리용품</t>
-  </si>
-  <si>
     <t>구강청결제</t>
   </si>
   <si>
-    <t>그물망이 부드러운 대형뜰채</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043786727</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958829/89588297426.jpg</t>
-  </si>
-  <si>
     <t>도그다</t>
   </si>
   <si>
-    <t>반려동물용 펫퍼스 안구세정제 120ml</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043785504</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958829/89588296203.jpg</t>
-  </si>
-  <si>
-    <t>펫퍼스</t>
-  </si>
-  <si>
-    <t>강아지 훈련용 초크체인 1호 1P 목줄 산책 목걸이</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043785572</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958829/89588296271.jpg</t>
-  </si>
-  <si>
-    <t>그루머스</t>
-  </si>
-  <si>
     <t>강아지 장난감/훈련</t>
   </si>
   <si>
-    <t>훈련용품</t>
-  </si>
-  <si>
-    <t>강아지 훈련소 훈련&lt;b&gt;용품&lt;/b&gt; 점프 반면 타일 1개 블루</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043784931</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958829/89588295630.jpg</t>
-  </si>
-  <si>
-    <t>오마이픽 스토어</t>
-  </si>
-  <si>
-    <t>강아지 &lt;b&gt;애완&lt;/b&gt;견 배변판 토일렛 화장실 민트</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043784341</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958829/89588295040.jpg</t>
-  </si>
-  <si>
     <t>배변판</t>
   </si>
   <si>
-    <t>천연소나무향 톱밥(35x12x9cm)</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043784069</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958829/89588294768.jpg</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;애완&lt;/b&gt;동물 안전문 게이트 강아지 고양이 현관 &lt;b&gt;애완&lt;/b&gt;견 출입문 격리</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043783577</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958829/89588294276.jpg</t>
-  </si>
-  <si>
-    <t>오팔리네</t>
-  </si>
-  <si>
-    <t>안전문</t>
-  </si>
-  <si>
-    <t>아몬스 강아지 기저귀 애견 귀저기 초미니형 10매</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043781992</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958829/89588292691.jpg</t>
-  </si>
-  <si>
-    <t>기저귀/팬티</t>
-  </si>
-  <si>
-    <t>스텐드 식기물병 벽걸이물병 강아지 고양이 애견 &lt;b&gt;용품&lt;/b&gt; 브라운</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043781294</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958829/89588291993.jpg</t>
-  </si>
-  <si>
-    <t>메리go라운드</t>
-  </si>
-  <si>
-    <t>빌리</t>
-  </si>
-  <si>
-    <t>식기/급수기</t>
-  </si>
-  <si>
-    <t>식기/식탁</t>
-  </si>
-  <si>
-    <t>강아지 목 보호대 쿠션 애견 넥카라 깔대기 KL 아쿠아폭스(M)</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043781239</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958829/89588291938.jpg</t>
-  </si>
-  <si>
-    <t>PAT</t>
-  </si>
-  <si>
-    <t>기타 미용/목욕용품</t>
-  </si>
-  <si>
-    <t>세라믹 &lt;b&gt;애완&lt;/b&gt;동물 유골함 강아지 관 추모품 사망한 강아지용 1. Red strawberry</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043781105</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958829/89588291804.jpg</t>
-  </si>
-  <si>
-    <t>성상트레이딩16호점</t>
-  </si>
-  <si>
-    <t>서비스</t>
-  </si>
-  <si>
-    <t>장례용품</t>
-  </si>
-  <si>
-    <t>고양이 강아지 털 개털 머리카락 먼지 청소 스크래퍼</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043780910</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958829/89588291609.jpg</t>
-  </si>
-  <si>
-    <t>대형견 계단 승강기 블랙 차량계단 30 GORILLA &lt;b&gt;애완&lt;/b&gt;동물 고양이계단 쿠션 원목 보호</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043780762</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958829/89588291461.jpg</t>
-  </si>
-  <si>
-    <t>물류에세이2</t>
-  </si>
-  <si>
-    <t>계단/스텝</t>
-  </si>
-  <si>
-    <t>테비 사사미 1kg 오리가슴살 개간식 반려동물 &lt;b&gt;애완용품&lt;/b&gt; 훈련용</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043778999</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958828/89588289698.jpg</t>
-  </si>
-  <si>
-    <t>프 리 즘</t>
-  </si>
-  <si>
-    <t>육포/건조간식</t>
-  </si>
-  <si>
-    <t>와인앤쿡캣잎 흡착 브러쉬 셀프 그루밍</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043778405</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958828/89588289104.jpg</t>
-  </si>
-  <si>
     <t>현대Hmall</t>
   </si>
   <si>
     <t>교보문고</t>
-  </si>
-  <si>
-    <t>와인앤쿡수족관 인테리어 성벽 장식품</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043778134</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958828/89588288833.jpg</t>
-  </si>
-  <si>
-    <t>와인앤쿡파충류 먹이그릇 1구</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043778204</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958828/89588288903.jpg</t>
-  </si>
-  <si>
-    <t>와인앤쿡횟대 큐티 모이통 4색 컬러세트</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043777649</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958828/89588288348.jpg</t>
-  </si>
-  <si>
-    <t>똥삽 고양이 화장실 배변처리 일체형 모래삽 벤토나이 오렌지</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043585157</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958809/89588095858.jpg</t>
   </si>
   <si>
     <t>고양이 배변용품</t>
@@ -691,6 +438,224 @@
 - 반려동물 양육비는 월 19만원, 치료비는 2배 증가, 시장은 2022년~2024년 연평균 1.4% 성장.  
 - 애완용품 점포 수는 늘었지만 점당 매출은 감소, 시장은 연평균 1.4% 증가, 가맹점 4.2% 증가.  
 - 북한은 고급 와인, 명품시계, 애견용품 등 다양한 상품을 수입.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>펫포유 &lt;b&gt;포켄스&lt;/b&gt; 덴티페어리 베트 VET (동물병원전용) M(중형) 70g 5개</t>
+  </si>
+  <si>
+    <t>https://link.auction.co.kr/gate/pcs?item-no=F264422136&amp;sub-id=1&amp;service-code=10000003</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557987/55579876708.jpg</t>
+  </si>
+  <si>
+    <t>옥션</t>
+  </si>
+  <si>
+    <t>개껌</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;포켄스&lt;/b&gt; 덴티페어리 베트 VET 200g S X3개 (총600g)</t>
+  </si>
+  <si>
+    <t>https://link.gmarket.co.kr/gate/pcs?item-no=4461673000&amp;sub-id=1003&amp;service-code=10000003&amp;lcd=100000038</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557985/55579859939.jpg</t>
+  </si>
+  <si>
+    <t>G마켓</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;포켄스&lt;/b&gt; 덴티페어리 치석껌 양치껌 M(중형) 75g 2개</t>
+  </si>
+  <si>
+    <t>https://link.gmarket.co.kr/gate/pcs?item-no=4461672131&amp;sub-id=1003&amp;service-code=10000003&amp;lcd=100000038</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557984/55579843217.jpg</t>
+  </si>
+  <si>
+    <t>https://link.auction.co.kr/gate/pcs?item-no=F264423005&amp;sub-id=1&amp;service-code=10000003</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557983/55579837623.jpg</t>
+  </si>
+  <si>
+    <t>펫포유 &lt;b&gt;포켄스&lt;/b&gt; 덴티페어리 베트 VET (동물병원전용) S(소형) 70g 5개</t>
+  </si>
+  <si>
+    <t>https://link.gmarket.co.kr/gate/pcs?item-no=4461674600&amp;sub-id=1003&amp;service-code=10000003&amp;lcd=100000038</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557982/55579825410.jpg</t>
+  </si>
+  <si>
+    <t>https://link.auction.co.kr/gate/pcs?item-no=F264425786&amp;sub-id=1&amp;service-code=10000003</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557979/55579797058.jpg</t>
+  </si>
+  <si>
+    <t>https://link.auction.co.kr/gate/pcs?item-no=F264423819&amp;sub-id=1&amp;service-code=10000003</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557979/55579793345.jpg</t>
+  </si>
+  <si>
+    <t>https://link.gmarket.co.kr/gate/pcs?item-no=4461671198&amp;sub-id=1003&amp;service-code=10000003&amp;lcd=100000038</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557979/55579791835.jpg</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;포켄스&lt;/b&gt; 덴탈스틱220g 오메가3 칼슘 블루베리 덴탈껌</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12044063790</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958857/89588574489.jpg</t>
+  </si>
+  <si>
+    <t>팔리복스66</t>
+  </si>
+  <si>
+    <t>포켄스</t>
+  </si>
+  <si>
+    <t>강아지껌 &lt;b&gt;포켄스&lt;/b&gt; 덴티 페어리 75g L 특식 영양식</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12044048136</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958855/89588558835.jpg</t>
+  </si>
+  <si>
+    <t>힐링짱</t>
+  </si>
+  <si>
+    <t>NEW&lt;b&gt;포켄스&lt;/b&gt; 카누들 덴탈껌 S 100p 1+1 -</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043920449</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958843/89588431148.jpg</t>
+  </si>
+  <si>
+    <t>클린Health</t>
+  </si>
+  <si>
+    <t>고양이 간식</t>
+  </si>
+  <si>
+    <t>동결건조 간식</t>
+  </si>
+  <si>
+    <t>덴티페어리 벌크팩 SS 217개입 1.02kg &lt;b&gt;포켄스&lt;/b&gt; 강아지덴탈껌 치석 입냄새 감소 높은 기호성</t>
+  </si>
+  <si>
+    <t>https://link.auction.co.kr/gate/pcs?item-no=F264376267&amp;sub-id=1&amp;service-code=10000003</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557943/55579432858.jpg</t>
+  </si>
+  <si>
+    <t>https://link.gmarket.co.kr/gate/pcs?item-no=4149710046&amp;sub-id=1003&amp;service-code=10000003&amp;lcd=100000038</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557938/55579386777.jpg</t>
+  </si>
+  <si>
+    <t>서락 &lt;b&gt;포켄스&lt;/b&gt; 덴티 페어리 65g 입냄세제거 대형견개껌 강아지껌 강아지간식</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043630283</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958814/89588140982.jpg</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;포켄스&lt;/b&gt; 덴티 페어리 65g (S) (강아지 간식)</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043833423</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958834/89588344122.jpg</t>
+  </si>
+  <si>
+    <t>아르덴랜드</t>
+  </si>
+  <si>
+    <t>서락 &lt;b&gt;포켄스&lt;/b&gt; 과일먹은 치즈덴탈껌 딸기 맛있는간식 애견과일껌 맛좋은강아지간식</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043805235</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958831/89588315934.jpg</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;포켄스&lt;/b&gt; 화이트닝 샴푸 1000ml 선택</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043794418</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958830/89588305117.jpg</t>
+  </si>
+  <si>
+    <t>샴푸/린스/비누</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043693959</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958820/89588204658.jpg</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;포켄스&lt;/b&gt; 뉴트리션 트릿 면역 영양 240g관 보충 저키 강아지져 져키</t>
+  </si>
+  <si>
+    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=8431919085&amp;tid=1000000061</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557930/55579303499.jpg</t>
+  </si>
+  <si>
+    <t>11번가</t>
+  </si>
+  <si>
+    <t>트릿/스틱</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;포켄스&lt;/b&gt; 덴티페어리 SS 디스펜서 (124p) 강아지 덴탈껌</t>
+  </si>
+  <si>
+    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=7898487960&amp;tid=1000000061</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557929/55579294213.jpg</t>
+  </si>
+  <si>
+    <t>페슬러</t>
+  </si>
+  <si>
+    <t>2025-07-01 17:20:33 기준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최근 목록은 반려동물 배변용품·간식 중심에서 치과용품(덴티페어리), 미용샴푸, 청소용품 등 건강관리와 위생 용품으로 대체되었으며, 상품 가격은 1,100원부터 69,400원까지 다양해졌고, 쇼핑몰도 변경되어 옥션·G마켓·11번가 등으로 다변화됐습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 포켄스(FORCANS)는 2025년 3월 7일, 소형견 맞춤 '미니바이츠' 덴탈껌(사이즈 S, SS) 2종을 출시. 
+- 고객 관찰 분석 후 별도 쪼갤 필요 없이 370개 제품 판매로 인기.
+- 온라인 할인 행사와 이벤트 통해 제품 판매 촉진, 2024년부터 마케팅 전략 강화.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1195,7 +1160,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
@@ -1203,9 +1168,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="19.2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:1" ht="57.6" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -1214,9 +1179,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:1" s="3" customFormat="1" ht="115.2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:1" s="3" customFormat="1" ht="76.8" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1192,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A216B37A-CDEF-4B8E-85BA-9DC942EA39C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84332D04-46BF-4775-A676-AFD08174531A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1244,7 +1209,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
-        <v>25</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
@@ -1252,9 +1217,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="403.2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:1" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -1263,9 +1228,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:1" s="3" customFormat="1" ht="172.8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:1" s="3" customFormat="1" ht="115.2" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1288,33 +1253,33 @@
   <sheetData>
     <row r="1" spans="1:1" ht="36" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="384" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="7" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:1" s="3" customFormat="1" ht="230.4" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1381,22 +1346,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E2">
-        <v>57480</v>
+        <v>34700</v>
       </c>
       <c r="G2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="H2">
-        <v>89588404320</v>
+        <v>55579876708</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -1408,10 +1373,10 @@
         <v>19</v>
       </c>
       <c r="N2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="O2" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
@@ -1419,22 +1384,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E3">
-        <v>15000</v>
+        <v>69400</v>
       </c>
       <c r="G3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H3">
-        <v>89588437193</v>
+        <v>55579859939</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -1446,7 +1411,10 @@
         <v>19</v>
       </c>
       <c r="N3" t="s">
-        <v>21</v>
+        <v>29</v>
+      </c>
+      <c r="O3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.4">
@@ -1454,29 +1422,26 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C4" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D4" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E4">
-        <v>2130</v>
+        <v>18200</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>138</v>
       </c>
       <c r="H4">
-        <v>89588314106</v>
+        <v>55579843217</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
-      <c r="K4" t="s">
-        <v>132</v>
-      </c>
       <c r="L4" t="s">
         <v>18</v>
       </c>
@@ -1484,10 +1449,10 @@
         <v>19</v>
       </c>
       <c r="N4" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="O4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.4">
@@ -1495,37 +1460,37 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E5">
+        <v>18300</v>
+      </c>
+      <c r="G5" t="s">
+        <v>133</v>
+      </c>
+      <c r="H5">
+        <v>55579837623</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="L5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" t="s">
         <v>134</v>
-      </c>
-      <c r="C5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E5">
-        <v>1880</v>
-      </c>
-      <c r="G5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H5">
-        <v>89588436097</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="L5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" t="s">
-        <v>19</v>
-      </c>
-      <c r="N5" t="s">
-        <v>119</v>
-      </c>
-      <c r="O5" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.4">
@@ -1533,22 +1498,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E6">
+        <v>34400</v>
+      </c>
+      <c r="G6" t="s">
         <v>138</v>
       </c>
-      <c r="D6" t="s">
-        <v>139</v>
-      </c>
-      <c r="E6">
-        <v>5780</v>
-      </c>
-      <c r="G6" t="s">
-        <v>140</v>
-      </c>
       <c r="H6">
-        <v>89588435755</v>
+        <v>55579825410</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -1560,10 +1525,10 @@
         <v>19</v>
       </c>
       <c r="N6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="O6" t="s">
-        <v>36</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.4">
@@ -1571,29 +1536,26 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E7">
-        <v>2000</v>
+        <v>34700</v>
       </c>
       <c r="G7" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="H7">
-        <v>89588305151</v>
+        <v>55579797058</v>
       </c>
       <c r="I7">
         <v>2</v>
       </c>
-      <c r="K7" t="s">
-        <v>106</v>
-      </c>
       <c r="L7" t="s">
         <v>18</v>
       </c>
@@ -1601,10 +1563,10 @@
         <v>19</v>
       </c>
       <c r="N7" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="O7" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.4">
@@ -1612,29 +1574,26 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D8" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E8">
-        <v>8380</v>
+        <v>70100</v>
       </c>
       <c r="G8" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="H8">
-        <v>89588433170</v>
+        <v>55579793345</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
-      <c r="K8" t="s">
-        <v>149</v>
-      </c>
       <c r="L8" t="s">
         <v>18</v>
       </c>
@@ -1642,7 +1601,10 @@
         <v>19</v>
       </c>
       <c r="N8" t="s">
-        <v>21</v>
+        <v>29</v>
+      </c>
+      <c r="O8" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
@@ -1650,7 +1612,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C9" t="s">
         <v>151</v>
@@ -1659,13 +1621,13 @@
         <v>152</v>
       </c>
       <c r="E9">
-        <v>51900</v>
+        <v>34400</v>
       </c>
       <c r="G9" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="H9">
-        <v>89588433426</v>
+        <v>55579791835</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -1677,10 +1639,10 @@
         <v>19</v>
       </c>
       <c r="N9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="O9" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.4">
@@ -1688,37 +1650,40 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C10" t="s">
         <v>154</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>155</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10">
+        <v>20300</v>
+      </c>
+      <c r="G10" t="s">
         <v>156</v>
       </c>
-      <c r="E10">
-        <v>9900</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="H10">
+        <v>89588574489</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10" t="s">
         <v>157</v>
       </c>
-      <c r="H10">
-        <v>89588302111</v>
-      </c>
-      <c r="I10">
-        <v>2</v>
+      <c r="K10" t="s">
+        <v>157</v>
       </c>
       <c r="L10" t="s">
         <v>18</v>
       </c>
       <c r="M10" t="s">
-        <v>158</v>
+        <v>19</v>
       </c>
       <c r="N10" t="s">
-        <v>159</v>
-      </c>
-      <c r="O10" t="s">
-        <v>160</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.4">
@@ -1726,22 +1691,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" t="s">
+        <v>160</v>
+      </c>
+      <c r="E11">
+        <v>6940</v>
+      </c>
+      <c r="G11" t="s">
         <v>161</v>
       </c>
-      <c r="C11" t="s">
-        <v>162</v>
-      </c>
-      <c r="D11" t="s">
-        <v>163</v>
-      </c>
-      <c r="E11">
-        <v>76330</v>
-      </c>
-      <c r="G11" t="s">
-        <v>164</v>
-      </c>
       <c r="H11">
-        <v>89588432654</v>
+        <v>89588558835</v>
       </c>
       <c r="I11">
         <v>2</v>
@@ -1753,7 +1718,10 @@
         <v>19</v>
       </c>
       <c r="N11" t="s">
-        <v>21</v>
+        <v>29</v>
+      </c>
+      <c r="O11" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.4">
@@ -1761,34 +1729,43 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E12">
+        <v>67400</v>
+      </c>
+      <c r="G12" t="s">
         <v>165</v>
       </c>
-      <c r="C12" t="s">
+      <c r="H12">
+        <v>89588431148</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12" t="s">
+        <v>157</v>
+      </c>
+      <c r="K12" t="s">
+        <v>157</v>
+      </c>
+      <c r="L12" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" t="s">
+        <v>19</v>
+      </c>
+      <c r="N12" t="s">
         <v>166</v>
       </c>
-      <c r="D12" t="s">
+      <c r="O12" t="s">
         <v>167</v>
-      </c>
-      <c r="E12">
-        <v>16000</v>
-      </c>
-      <c r="G12" t="s">
-        <v>128</v>
-      </c>
-      <c r="H12">
-        <v>89588431561</v>
-      </c>
-      <c r="I12">
-        <v>2</v>
-      </c>
-      <c r="L12" t="s">
-        <v>18</v>
-      </c>
-      <c r="M12" t="s">
-        <v>19</v>
-      </c>
-      <c r="N12" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.4">
@@ -1805,20 +1782,17 @@
         <v>170</v>
       </c>
       <c r="E13">
-        <v>16650</v>
+        <v>72000</v>
       </c>
       <c r="G13" t="s">
-        <v>171</v>
+        <v>133</v>
       </c>
       <c r="H13">
-        <v>89588431280</v>
+        <v>55579432858</v>
       </c>
       <c r="I13">
         <v>2</v>
       </c>
-      <c r="K13" t="s">
-        <v>172</v>
-      </c>
       <c r="L13" t="s">
         <v>18</v>
       </c>
@@ -1826,10 +1800,10 @@
         <v>19</v>
       </c>
       <c r="N13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="O13" t="s">
-        <v>173</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.4">
@@ -1837,22 +1811,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C14" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D14" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E14">
-        <v>5500</v>
+        <v>64080</v>
       </c>
       <c r="G14" t="s">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="H14">
-        <v>89588388722</v>
+        <v>55579386777</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -1864,7 +1838,10 @@
         <v>19</v>
       </c>
       <c r="N14" t="s">
-        <v>21</v>
+        <v>29</v>
+      </c>
+      <c r="O14" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.4">
@@ -1872,22 +1849,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C15" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D15" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E15">
-        <v>60120</v>
+        <v>4920</v>
       </c>
       <c r="G15" t="s">
-        <v>181</v>
+        <v>42</v>
       </c>
       <c r="H15">
-        <v>89588430610</v>
+        <v>89588140982</v>
       </c>
       <c r="I15">
         <v>2</v>
@@ -1899,10 +1876,10 @@
         <v>19</v>
       </c>
       <c r="N15" t="s">
-        <v>119</v>
+        <v>29</v>
       </c>
       <c r="O15" t="s">
-        <v>182</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.4">
@@ -1910,22 +1887,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C16" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D16" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E16">
-        <v>11700</v>
+        <v>11490</v>
       </c>
       <c r="G16" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="H16">
-        <v>89588429695</v>
+        <v>89588344122</v>
       </c>
       <c r="I16">
         <v>2</v>
@@ -1937,10 +1914,10 @@
         <v>19</v>
       </c>
       <c r="N16" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="O16" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.4">
@@ -1948,22 +1925,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C17" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D17" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E17">
-        <v>237800</v>
+        <v>3360</v>
       </c>
       <c r="G17" t="s">
-        <v>191</v>
+        <v>42</v>
       </c>
       <c r="H17">
-        <v>89588429526</v>
+        <v>89588315934</v>
       </c>
       <c r="I17">
         <v>2</v>
@@ -1972,10 +1949,13 @@
         <v>18</v>
       </c>
       <c r="M17" t="s">
-        <v>192</v>
+        <v>19</v>
       </c>
       <c r="N17" t="s">
-        <v>193</v>
+        <v>29</v>
+      </c>
+      <c r="O17" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.4">
@@ -1983,26 +1963,32 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="C18" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="D18" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="E18">
-        <v>1080</v>
+        <v>18170</v>
       </c>
       <c r="G18" t="s">
-        <v>148</v>
+        <v>32</v>
       </c>
       <c r="H18">
-        <v>89588429160</v>
+        <v>89588305117</v>
       </c>
       <c r="I18">
         <v>2</v>
       </c>
+      <c r="J18" t="s">
+        <v>157</v>
+      </c>
+      <c r="K18" t="s">
+        <v>157</v>
+      </c>
       <c r="L18" t="s">
         <v>18</v>
       </c>
@@ -2010,10 +1996,10 @@
         <v>19</v>
       </c>
       <c r="N18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O18" t="s">
-        <v>133</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.4">
@@ -2021,22 +2007,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="C19" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="D19" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="E19">
-        <v>1570</v>
+        <v>11780</v>
       </c>
       <c r="G19" t="s">
-        <v>148</v>
+        <v>32</v>
       </c>
       <c r="H19">
-        <v>89588429164</v>
+        <v>89588204658</v>
       </c>
       <c r="I19">
         <v>2</v>
@@ -2048,10 +2034,10 @@
         <v>19</v>
       </c>
       <c r="N19" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="O19" t="s">
-        <v>200</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.4">
@@ -2059,22 +2045,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C20" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D20" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="E20">
-        <v>1570</v>
+        <v>19610</v>
       </c>
       <c r="G20" t="s">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="H20">
-        <v>89588429161</v>
+        <v>55579303499</v>
       </c>
       <c r="I20">
         <v>2</v>
@@ -2086,10 +2072,10 @@
         <v>19</v>
       </c>
       <c r="N20" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="O20" t="s">
-        <v>133</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.4">
@@ -2097,26 +2083,29 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C21" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="D21" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="E21">
-        <v>890</v>
+        <v>44160</v>
       </c>
       <c r="G21" t="s">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="H21">
-        <v>89588429167</v>
+        <v>55579294213</v>
       </c>
       <c r="I21">
         <v>2</v>
       </c>
+      <c r="J21" t="s">
+        <v>197</v>
+      </c>
       <c r="L21" t="s">
         <v>18</v>
       </c>
@@ -2124,10 +2113,10 @@
         <v>19</v>
       </c>
       <c r="N21" t="s">
-        <v>207</v>
+        <v>29</v>
       </c>
       <c r="O21" t="s">
-        <v>208</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2137,8 +2126,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C28800-3831-467E-8CF5-53CC2ABF0E18}">
-  <dimension ref="A1:O20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AC6ED0-1D7D-410B-8E53-3876EC6F573C}">
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.4">
@@ -2193,22 +2182,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E2">
-        <v>4130</v>
+        <v>57480</v>
       </c>
       <c r="G2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H2">
-        <v>89588297426</v>
+        <v>89588404320</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -2220,7 +2209,10 @@
         <v>19</v>
       </c>
       <c r="N2" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="O2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
@@ -2228,32 +2220,26 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E3">
-        <v>8230</v>
+        <v>15000</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H3">
-        <v>89588296203</v>
+        <v>89588437193</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
-      <c r="J3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K3" t="s">
-        <v>44</v>
-      </c>
       <c r="L3" t="s">
         <v>18</v>
       </c>
@@ -2261,10 +2247,7 @@
         <v>19</v>
       </c>
       <c r="N3" t="s">
-        <v>34</v>
-      </c>
-      <c r="O3" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.4">
@@ -2272,28 +2255,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E4">
-        <v>13200</v>
+        <v>2130</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H4">
-        <v>89588296271</v>
+        <v>89588314106</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
-      <c r="J4" t="s">
-        <v>48</v>
+      <c r="K4" t="s">
+        <v>50</v>
       </c>
       <c r="L4" t="s">
         <v>18</v>
@@ -2302,10 +2285,10 @@
         <v>19</v>
       </c>
       <c r="N4" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="O4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.4">
@@ -2313,22 +2296,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E5">
-        <v>282100</v>
+        <v>1880</v>
       </c>
       <c r="G5" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="H5">
-        <v>89588295630</v>
+        <v>89588436097</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -2340,10 +2323,10 @@
         <v>19</v>
       </c>
       <c r="N5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="O5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.4">
@@ -2360,13 +2343,13 @@
         <v>57</v>
       </c>
       <c r="E6">
-        <v>16570</v>
+        <v>5780</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="H6">
-        <v>89588295040</v>
+        <v>89588435755</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -2378,10 +2361,10 @@
         <v>19</v>
       </c>
       <c r="N6" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="O6" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.4">
@@ -2398,17 +2381,20 @@
         <v>61</v>
       </c>
       <c r="E7">
-        <v>4700</v>
+        <v>2000</v>
       </c>
       <c r="G7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H7">
-        <v>89588294768</v>
+        <v>89588305151</v>
       </c>
       <c r="I7">
         <v>2</v>
       </c>
+      <c r="K7" t="s">
+        <v>36</v>
+      </c>
       <c r="L7" t="s">
         <v>18</v>
       </c>
@@ -2416,7 +2402,10 @@
         <v>19</v>
       </c>
       <c r="N7" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="O7" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.4">
@@ -2424,26 +2413,29 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E8">
-        <v>35020</v>
+        <v>8380</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H8">
-        <v>89588294276</v>
+        <v>89588433170</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
+      <c r="K8" t="s">
+        <v>67</v>
+      </c>
       <c r="L8" t="s">
         <v>18</v>
       </c>
@@ -2451,10 +2443,7 @@
         <v>19</v>
       </c>
       <c r="N8" t="s">
-        <v>23</v>
-      </c>
-      <c r="O8" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
@@ -2462,22 +2451,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E9">
-        <v>8150</v>
+        <v>51900</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H9">
-        <v>89588292691</v>
+        <v>89588433426</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -2489,10 +2478,10 @@
         <v>19</v>
       </c>
       <c r="N9" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="O9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.4">
@@ -2500,40 +2489,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E10">
-        <v>14270</v>
+        <v>9900</v>
       </c>
       <c r="G10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H10">
-        <v>89588291993</v>
+        <v>89588302111</v>
       </c>
       <c r="I10">
         <v>2</v>
       </c>
-      <c r="J10" t="s">
-        <v>75</v>
-      </c>
       <c r="L10" t="s">
         <v>18</v>
       </c>
       <c r="M10" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="N10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.4">
@@ -2541,29 +2527,26 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E11">
-        <v>14970</v>
+        <v>76330</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="H11">
-        <v>89588291938</v>
+        <v>89588432654</v>
       </c>
       <c r="I11">
         <v>2</v>
       </c>
-      <c r="J11" t="s">
-        <v>81</v>
-      </c>
       <c r="L11" t="s">
         <v>18</v>
       </c>
@@ -2571,10 +2554,7 @@
         <v>19</v>
       </c>
       <c r="N11" t="s">
-        <v>20</v>
-      </c>
-      <c r="O11" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.4">
@@ -2591,13 +2571,13 @@
         <v>85</v>
       </c>
       <c r="E12">
-        <v>24740</v>
+        <v>16000</v>
       </c>
       <c r="G12" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H12">
-        <v>89588291804</v>
+        <v>89588431561</v>
       </c>
       <c r="I12">
         <v>2</v>
@@ -2609,10 +2589,7 @@
         <v>19</v>
       </c>
       <c r="N12" t="s">
-        <v>87</v>
-      </c>
-      <c r="O12" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.4">
@@ -2620,34 +2597,40 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13">
+        <v>16650</v>
+      </c>
+      <c r="G13" t="s">
         <v>89</v>
       </c>
-      <c r="C13" t="s">
+      <c r="H13">
+        <v>89588431280</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="K13" t="s">
         <v>90</v>
       </c>
-      <c r="D13" t="s">
+      <c r="L13" t="s">
+        <v>18</v>
+      </c>
+      <c r="M13" t="s">
+        <v>19</v>
+      </c>
+      <c r="N13" t="s">
+        <v>22</v>
+      </c>
+      <c r="O13" t="s">
         <v>91</v>
-      </c>
-      <c r="E13">
-        <v>6620</v>
-      </c>
-      <c r="G13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13">
-        <v>89588291609</v>
-      </c>
-      <c r="I13">
-        <v>2</v>
-      </c>
-      <c r="L13" t="s">
-        <v>18</v>
-      </c>
-      <c r="M13" t="s">
-        <v>19</v>
-      </c>
-      <c r="N13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.4">
@@ -2664,13 +2647,13 @@
         <v>94</v>
       </c>
       <c r="E14">
-        <v>64120</v>
+        <v>5500</v>
       </c>
       <c r="G14" t="s">
         <v>95</v>
       </c>
       <c r="H14">
-        <v>89588291461</v>
+        <v>89588388722</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -2682,10 +2665,7 @@
         <v>19</v>
       </c>
       <c r="N14" t="s">
-        <v>23</v>
-      </c>
-      <c r="O14" t="s">
-        <v>96</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.4">
@@ -2693,37 +2673,37 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" t="s">
         <v>97</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>98</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15">
+        <v>60120</v>
+      </c>
+      <c r="G15" t="s">
         <v>99</v>
       </c>
-      <c r="E15">
-        <v>20660</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="H15">
+        <v>89588430610</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="L15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M15" t="s">
+        <v>19</v>
+      </c>
+      <c r="N15" t="s">
+        <v>37</v>
+      </c>
+      <c r="O15" t="s">
         <v>100</v>
-      </c>
-      <c r="H15">
-        <v>89588289698</v>
-      </c>
-      <c r="I15">
-        <v>2</v>
-      </c>
-      <c r="L15" t="s">
-        <v>18</v>
-      </c>
-      <c r="M15" t="s">
-        <v>19</v>
-      </c>
-      <c r="N15" t="s">
-        <v>33</v>
-      </c>
-      <c r="O15" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.4">
@@ -2731,37 +2711,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" t="s">
         <v>102</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>103</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16">
+        <v>11700</v>
+      </c>
+      <c r="G16" t="s">
         <v>104</v>
       </c>
-      <c r="E16">
-        <v>8900</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="H16">
+        <v>89588429695</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="L16" t="s">
+        <v>18</v>
+      </c>
+      <c r="M16" t="s">
+        <v>19</v>
+      </c>
+      <c r="N16" t="s">
+        <v>33</v>
+      </c>
+      <c r="O16" t="s">
         <v>105</v>
-      </c>
-      <c r="H16">
-        <v>89588289104</v>
-      </c>
-      <c r="I16">
-        <v>2</v>
-      </c>
-      <c r="K16" t="s">
-        <v>106</v>
-      </c>
-      <c r="L16" t="s">
-        <v>18</v>
-      </c>
-      <c r="M16" t="s">
-        <v>19</v>
-      </c>
-      <c r="N16" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.4">
@@ -2769,37 +2749,34 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" t="s">
         <v>107</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>108</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17">
+        <v>237800</v>
+      </c>
+      <c r="G17" t="s">
         <v>109</v>
       </c>
-      <c r="E17">
-        <v>20800</v>
-      </c>
-      <c r="G17" t="s">
-        <v>105</v>
-      </c>
       <c r="H17">
-        <v>89588288833</v>
+        <v>89588429526</v>
       </c>
       <c r="I17">
         <v>2</v>
       </c>
-      <c r="K17" t="s">
-        <v>106</v>
-      </c>
       <c r="L17" t="s">
         <v>18</v>
       </c>
       <c r="M17" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="N17" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.4">
@@ -2807,29 +2784,26 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E18">
-        <v>13500</v>
+        <v>1080</v>
       </c>
       <c r="G18" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="H18">
-        <v>89588288903</v>
+        <v>89588429160</v>
       </c>
       <c r="I18">
         <v>2</v>
       </c>
-      <c r="K18" t="s">
-        <v>106</v>
-      </c>
       <c r="L18" t="s">
         <v>18</v>
       </c>
@@ -2837,7 +2811,10 @@
         <v>19</v>
       </c>
       <c r="N18" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="O18" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.4">
@@ -2845,29 +2822,26 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E19">
-        <v>12900</v>
+        <v>1570</v>
       </c>
       <c r="G19" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="H19">
-        <v>89588288348</v>
+        <v>89588429164</v>
       </c>
       <c r="I19">
         <v>2</v>
       </c>
-      <c r="K19" t="s">
-        <v>106</v>
-      </c>
       <c r="L19" t="s">
         <v>18</v>
       </c>
@@ -2875,7 +2849,10 @@
         <v>19</v>
       </c>
       <c r="N19" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="O19" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.4">
@@ -2883,22 +2860,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E20">
-        <v>17280</v>
+        <v>1570</v>
       </c>
       <c r="G20" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="H20">
-        <v>89588095858</v>
+        <v>89588429161</v>
       </c>
       <c r="I20">
         <v>2</v>
@@ -2910,10 +2887,48 @@
         <v>19</v>
       </c>
       <c r="N20" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
       <c r="O20" t="s">
-        <v>120</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21" t="s">
+        <v>124</v>
+      </c>
+      <c r="E21">
+        <v>890</v>
+      </c>
+      <c r="G21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21">
+        <v>89588429167</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
+      </c>
+      <c r="L21" t="s">
+        <v>18</v>
+      </c>
+      <c r="M21" t="s">
+        <v>19</v>
+      </c>
+      <c r="N21" t="s">
+        <v>125</v>
+      </c>
+      <c r="O21" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/source/09_GenerativeAI_RPA/genai_rpa.xlsx
+++ b/source/09_GenerativeAI_RPA/genai_rpa.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai_x\source\09_GenerativeAI_RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2422930-4635-40B2-ABA2-E56477744678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D5054CA-96EF-46B6-9751-80084EF447DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="origin_report" sheetId="26" r:id="rId1"/>
     <sheet name="now_report" sheetId="205" r:id="rId2"/>
-    <sheet name="prev_report" sheetId="212" r:id="rId3"/>
+    <sheet name="prev_report" sheetId="216" r:id="rId3"/>
     <sheet name="now_report_en" sheetId="206" r:id="rId4"/>
     <sheet name="now_list" sheetId="204" r:id="rId5"/>
-    <sheet name="prev_list" sheetId="211" r:id="rId6"/>
+    <sheet name="prev_list" sheetId="215" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="104">
   <si>
     <t>OOO 일일 동향 보고서</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -99,9 +99,6 @@
   </si>
   <si>
     <t>기타반려동물용품</t>
-  </si>
-  <si>
-    <t>강아지 배변용품</t>
   </si>
   <si>
     <t>OO Daily Insights</t>
@@ -134,528 +131,241 @@
     <t>강아지 간식</t>
   </si>
   <si>
-    <t>강아지 건강/관리용품</t>
-  </si>
-  <si>
-    <t>구강청결제</t>
-  </si>
-  <si>
     <t>도그다</t>
   </si>
   <si>
-    <t>강아지 장난감/훈련</t>
-  </si>
-  <si>
-    <t>배변판</t>
-  </si>
-  <si>
-    <t>현대Hmall</t>
-  </si>
-  <si>
-    <t>교보문고</t>
-  </si>
-  <si>
-    <t>고양이 배변용품</t>
-  </si>
-  <si>
-    <t>분변통/모래삽</t>
-  </si>
-  <si>
-    <t>서락 쥬쥬베 실리콘 그물망 토일렛 SET 그린 배변&lt;b&gt;용품&lt;/b&gt; 배변 실리콘그물망화장실</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043893622</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958840/89588404320.jpg</t>
-  </si>
-  <si>
     <t>모두의 서락</t>
   </si>
   <si>
-    <t>바이탈밀 후르츠맛 50g - 도마뱀 사료,크레 먹이,파충류 슈퍼푸드 (크레스티드게코,가고일게코,리키에너스)</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043926494</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958843/89588437193.jpg</t>
-  </si>
-  <si>
-    <t>도마뱀용품점</t>
-  </si>
-  <si>
-    <t>쥬쥬베 배변봉투 리필 90매 (랜덤발송)</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043803407</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958831/89588314106.jpg</t>
-  </si>
-  <si>
-    <t>위버스코리아</t>
-  </si>
-  <si>
-    <t>배변봉투/집게</t>
-  </si>
-  <si>
-    <t>서락 티티펫 파스텔 컬러 고양이 삽 파스텔삽</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043925398</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958843/89588436097.jpg</t>
-  </si>
-  <si>
-    <t>칫솔 인기 애견</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043925056</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958843/89588435755.jpg</t>
-  </si>
-  <si>
-    <t>여누세마켓</t>
-  </si>
-  <si>
-    <t>아트박스 팝아트 핸드크림 피치젤리</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043794453</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958830/89588305151.jpg</t>
-  </si>
-  <si>
-    <t>배변패드</t>
-  </si>
-  <si>
-    <t>강아지 미세먼지 마스크 3개입 애견 반려견 3중 필터 스트랩 마스크 중형</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043922472</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958843/89588433170.jpg</t>
-  </si>
-  <si>
-    <t>아랑존디</t>
-  </si>
-  <si>
-    <t>바이온</t>
-  </si>
-  <si>
-    <t>서락 시저 쇠고기 100g 24개 강아지간식 &lt;b&gt;애완&lt;/b&gt;동물용 애견&lt;b&gt;용품&lt;/b&gt; 강아지육포간식</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043922727</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958843/89588433426.jpg</t>
-  </si>
-  <si>
-    <t>캔/파우치</t>
-  </si>
-  <si>
-    <t>창 풍경 스티커 장식 정크 저널 콜라주 편지지 &lt;b&gt;애완&lt;/b&gt; 동물 스크랩북 1. A</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043791412</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958830/89588302111.jpg</t>
-  </si>
-  <si>
-    <t>가온라온12호점</t>
-  </si>
-  <si>
-    <t>문구/사무용품</t>
-  </si>
-  <si>
-    <t>스티커/테이프</t>
-  </si>
-  <si>
-    <t>스티커</t>
-  </si>
-  <si>
-    <t>투명 옷걸이 진열대 반려동물 걸이 진주니켈</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043921955</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958843/89588432654.jpg</t>
-  </si>
-  <si>
-    <t>아크아크샵</t>
-  </si>
-  <si>
-    <t>바이탈밀 인섹트맛 80g - 도마뱀 사료,크레 먹이,파충류 슈퍼푸드 (크레스티드게코,가고일게코,리키에너스)</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043920862</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958843/89588431561.jpg</t>
-  </si>
-  <si>
-    <t>[HN2] 반려동물 탈취제 냄새제거 은나노탈취제 라벤더향</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043920581</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958843/89588431280.jpg</t>
-  </si>
-  <si>
-    <t>해븐하트</t>
-  </si>
-  <si>
-    <t>펫앤드림</t>
-  </si>
-  <si>
-    <t>탈취제/소독제</t>
-  </si>
-  <si>
-    <t>보관 곤충 파충류 채집통 다슬기 관찰통 케이스 중 사슴벌레</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043878023</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958838/89588388722.jpg</t>
-  </si>
-  <si>
-    <t>딩거의추천샵</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;애완&lt;/b&gt;동물 쓰레기통으로 교체하는 4Pcs 활성탄 필터, 공기 필터용 6 x 인치 교체 냄새 필터</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043919911</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958843/89588430610.jpg</t>
-  </si>
-  <si>
-    <t>핫딜마켓샵</t>
-  </si>
-  <si>
-    <t>자동화장실</t>
-  </si>
-  <si>
-    <t>고양이와 개 &lt;b&gt;애완&lt;/b&gt; 동물 플러시 공룡 장난감 파괴 할 수없는 씹는 작은 큰 개를위한 삐걱 거리는 소리 &lt;b&gt;용품&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043918996</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958842/89588429695.jpg</t>
-  </si>
-  <si>
-    <t>보시</t>
-  </si>
-  <si>
-    <t>장난감/토이</t>
-  </si>
-  <si>
-    <t>프리미엄 창문 스크린 DIY 키트 39 x 51 비 &lt;b&gt;애완&lt;/b&gt;동물 긁힘 꽃가루 미세먼지 99 30메쉬 내구성 신소재 도구 포함 폭 길이 190 51in X 190in-KIT</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043918827</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958842/89588429526.jpg</t>
-  </si>
-  <si>
-    <t>비에치22번가</t>
-  </si>
-  <si>
-    <t>청소용품</t>
-  </si>
-  <si>
-    <t>기타청소용품</t>
-  </si>
-  <si>
-    <t>생분해 반려동물 배변봉투 강아지 고양이 산책 위생봉투 풉백</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043918461</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958842/89588429160.jpg</t>
-  </si>
-  <si>
-    <t>반려동물 위생 눈꼽빗 스테인리스 이물질 제거 강아지 고양이 겸용 애견&lt;b&gt;용품&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043918465</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958842/89588429164.jpg</t>
-  </si>
-  <si>
-    <t>브러시/빗</t>
-  </si>
-  <si>
-    <t>반려동물 배변봉투 풉백 디스펜서 휴대용 캡슐형 강아지 산책용</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043918462</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958842/89588429161.jpg</t>
-  </si>
-  <si>
-    <t>반려동물 손가락 칫솔 강아지 고양이 투명 실리콘 구강 위생 관리</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043918471</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958842/89588429167.jpg</t>
-  </si>
-  <si>
-    <t>고양이 건강/관리용품</t>
-  </si>
-  <si>
-    <t>구강관리용품</t>
-  </si>
-  <si>
-    <t>2025-07-01 16:28:30 기준</t>
+    <t>펫포유 &lt;b&gt;포켄스&lt;/b&gt; 덴티페어리 베트 VET (동물병원전용) M(중형) 70g 5개</t>
+  </si>
+  <si>
+    <t>https://link.auction.co.kr/gate/pcs?item-no=F264422136&amp;sub-id=1&amp;service-code=10000003</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557987/55579876708.jpg</t>
+  </si>
+  <si>
+    <t>옥션</t>
+  </si>
+  <si>
+    <t>개껌</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;포켄스&lt;/b&gt; 덴티페어리 베트 VET 200g S X3개 (총600g)</t>
+  </si>
+  <si>
+    <t>https://link.gmarket.co.kr/gate/pcs?item-no=4461673000&amp;sub-id=1003&amp;service-code=10000003&amp;lcd=100000038</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557985/55579859939.jpg</t>
+  </si>
+  <si>
+    <t>G마켓</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;포켄스&lt;/b&gt; 덴티페어리 치석껌 양치껌 M(중형) 75g 2개</t>
+  </si>
+  <si>
+    <t>https://link.gmarket.co.kr/gate/pcs?item-no=4461672131&amp;sub-id=1003&amp;service-code=10000003&amp;lcd=100000038</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557984/55579843217.jpg</t>
+  </si>
+  <si>
+    <t>https://link.auction.co.kr/gate/pcs?item-no=F264423005&amp;sub-id=1&amp;service-code=10000003</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557983/55579837623.jpg</t>
+  </si>
+  <si>
+    <t>펫포유 &lt;b&gt;포켄스&lt;/b&gt; 덴티페어리 베트 VET (동물병원전용) S(소형) 70g 5개</t>
+  </si>
+  <si>
+    <t>https://link.gmarket.co.kr/gate/pcs?item-no=4461674600&amp;sub-id=1003&amp;service-code=10000003&amp;lcd=100000038</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557982/55579825410.jpg</t>
+  </si>
+  <si>
+    <t>https://link.auction.co.kr/gate/pcs?item-no=F264425786&amp;sub-id=1&amp;service-code=10000003</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557979/55579797058.jpg</t>
+  </si>
+  <si>
+    <t>https://link.auction.co.kr/gate/pcs?item-no=F264423819&amp;sub-id=1&amp;service-code=10000003</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557979/55579793345.jpg</t>
+  </si>
+  <si>
+    <t>https://link.gmarket.co.kr/gate/pcs?item-no=4461671198&amp;sub-id=1003&amp;service-code=10000003&amp;lcd=100000038</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557979/55579791835.jpg</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;포켄스&lt;/b&gt; 덴탈스틱220g 오메가3 칼슘 블루베리 덴탈껌</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12044063790</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958857/89588574489.jpg</t>
+  </si>
+  <si>
+    <t>팔리복스66</t>
+  </si>
+  <si>
+    <t>포켄스</t>
+  </si>
+  <si>
+    <t>강아지껌 &lt;b&gt;포켄스&lt;/b&gt; 덴티 페어리 75g L 특식 영양식</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12044048136</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958855/89588558835.jpg</t>
+  </si>
+  <si>
+    <t>힐링짱</t>
+  </si>
+  <si>
+    <t>NEW&lt;b&gt;포켄스&lt;/b&gt; 카누들 덴탈껌 S 100p 1+1 -</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043920449</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958843/89588431148.jpg</t>
+  </si>
+  <si>
+    <t>클린Health</t>
+  </si>
+  <si>
+    <t>고양이 간식</t>
+  </si>
+  <si>
+    <t>동결건조 간식</t>
+  </si>
+  <si>
+    <t>덴티페어리 벌크팩 SS 217개입 1.02kg &lt;b&gt;포켄스&lt;/b&gt; 강아지덴탈껌 치석 입냄새 감소 높은 기호성</t>
+  </si>
+  <si>
+    <t>https://link.auction.co.kr/gate/pcs?item-no=F264376267&amp;sub-id=1&amp;service-code=10000003</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557943/55579432858.jpg</t>
+  </si>
+  <si>
+    <t>https://link.gmarket.co.kr/gate/pcs?item-no=4149710046&amp;sub-id=1003&amp;service-code=10000003&amp;lcd=100000038</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557938/55579386777.jpg</t>
+  </si>
+  <si>
+    <t>서락 &lt;b&gt;포켄스&lt;/b&gt; 덴티 페어리 65g 입냄세제거 대형견개껌 강아지껌 강아지간식</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043630283</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958814/89588140982.jpg</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;포켄스&lt;/b&gt; 덴티 페어리 65g (S) (강아지 간식)</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043833423</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958834/89588344122.jpg</t>
+  </si>
+  <si>
+    <t>아르덴랜드</t>
+  </si>
+  <si>
+    <t>서락 &lt;b&gt;포켄스&lt;/b&gt; 과일먹은 치즈덴탈껌 딸기 맛있는간식 애견과일껌 맛좋은강아지간식</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043805235</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958831/89588315934.jpg</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;포켄스&lt;/b&gt; 화이트닝 샴푸 1000ml 선택</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043794418</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958830/89588305117.jpg</t>
+  </si>
+  <si>
+    <t>샴푸/린스/비누</t>
+  </si>
+  <si>
+    <t>https://smartstore.naver.com/main/products/12043693959</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_8958820/89588204658.jpg</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;포켄스&lt;/b&gt; 뉴트리션 트릿 면역 영양 240g관 보충 저키 강아지져 져키</t>
+  </si>
+  <si>
+    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=8431919085&amp;tid=1000000061</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5557930/55579303499.jpg</t>
+  </si>
+  <si>
+    <t>11번가</t>
+  </si>
+  <si>
+    <t>트릿/스틱</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;포켄스&lt;/b&gt; 덴탈스틱 후레시 칼슘(작은별)220g</t>
+  </si>
+  <si>
+    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=8432302645&amp;tid=1000000061</t>
+  </si>
+  <si>
+    <t>https://shopping-phinf.pstatic.net/main_5558002/55580027908.jpg</t>
+  </si>
+  <si>
+    <t>2025-07-01 17:47:45 기준</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>신상품 배변용품, 파충류 사료 등장하며 가격↑, 브랜드 및 카테고리도 변경됨.</t>
+    <t>이번 변경에서 '포켄스' 제품은 덴티페어리 베트 제품이 유지되고, 치석껌 등 일부 제품 가격이 소폭 조정됐으며, 신상품인 '포켄스 덴티스틱 후레시 칼슘 220g'이 새로 추가되었습니다. 전체 상품구성은 유사하나, 포켄스 관련 상품이 늘어난 점이 특징입니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 한국 기술과 생산품이 미국·중국, 러시아 등에서 인기, 2025년 1분기 생활 필수품 수요는 전년대비 2배 성장.  
-- 인천 반값택배 이용 소상공인 32.7%, 매출 증가 효과 확인.  
-- 반려동물 양육비는 월 19만원, 치료비는 2배 증가, 시장은 2022년~2024년 연평균 1.4% 성장.  
-- 애완용품 점포 수는 늘었지만 점당 매출은 감소, 시장은 연평균 1.4% 증가, 가맹점 4.2% 증가.  
-- 북한은 고급 와인, 명품시계, 애견용품 등 다양한 상품을 수입.</t>
+    <t>- 포켄스, 2025년 3월 7일 ‘미니바이츠’ 출시, S·SS 두 크기.  
+- 2025년 3월 10일, 소형견용 덴탈껌 인정받아.  
+- 제품 가격과 구체적 수치는 기사 내 언급 없음.  
+- ‘미니바이츠’는 소형 반려견  관심 집중.  
+- 2024년 9월 기준, ‘포켄스’는 강아지 덴탈껌 판매량 500만개 돌파.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>펫포유 &lt;b&gt;포켄스&lt;/b&gt; 덴티페어리 베트 VET (동물병원전용) M(중형) 70g 5개</t>
-  </si>
-  <si>
-    <t>https://link.auction.co.kr/gate/pcs?item-no=F264422136&amp;sub-id=1&amp;service-code=10000003</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5557987/55579876708.jpg</t>
-  </si>
-  <si>
-    <t>옥션</t>
-  </si>
-  <si>
-    <t>개껌</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;포켄스&lt;/b&gt; 덴티페어리 베트 VET 200g S X3개 (총600g)</t>
-  </si>
-  <si>
-    <t>https://link.gmarket.co.kr/gate/pcs?item-no=4461673000&amp;sub-id=1003&amp;service-code=10000003&amp;lcd=100000038</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5557985/55579859939.jpg</t>
-  </si>
-  <si>
-    <t>G마켓</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;포켄스&lt;/b&gt; 덴티페어리 치석껌 양치껌 M(중형) 75g 2개</t>
-  </si>
-  <si>
-    <t>https://link.gmarket.co.kr/gate/pcs?item-no=4461672131&amp;sub-id=1003&amp;service-code=10000003&amp;lcd=100000038</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5557984/55579843217.jpg</t>
-  </si>
-  <si>
-    <t>https://link.auction.co.kr/gate/pcs?item-no=F264423005&amp;sub-id=1&amp;service-code=10000003</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5557983/55579837623.jpg</t>
-  </si>
-  <si>
-    <t>펫포유 &lt;b&gt;포켄스&lt;/b&gt; 덴티페어리 베트 VET (동물병원전용) S(소형) 70g 5개</t>
-  </si>
-  <si>
-    <t>https://link.gmarket.co.kr/gate/pcs?item-no=4461674600&amp;sub-id=1003&amp;service-code=10000003&amp;lcd=100000038</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5557982/55579825410.jpg</t>
-  </si>
-  <si>
-    <t>https://link.auction.co.kr/gate/pcs?item-no=F264425786&amp;sub-id=1&amp;service-code=10000003</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5557979/55579797058.jpg</t>
-  </si>
-  <si>
-    <t>https://link.auction.co.kr/gate/pcs?item-no=F264423819&amp;sub-id=1&amp;service-code=10000003</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5557979/55579793345.jpg</t>
-  </si>
-  <si>
-    <t>https://link.gmarket.co.kr/gate/pcs?item-no=4461671198&amp;sub-id=1003&amp;service-code=10000003&amp;lcd=100000038</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5557979/55579791835.jpg</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;포켄스&lt;/b&gt; 덴탈스틱220g 오메가3 칼슘 블루베리 덴탈껌</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12044063790</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958857/89588574489.jpg</t>
-  </si>
-  <si>
-    <t>팔리복스66</t>
-  </si>
-  <si>
-    <t>포켄스</t>
-  </si>
-  <si>
-    <t>강아지껌 &lt;b&gt;포켄스&lt;/b&gt; 덴티 페어리 75g L 특식 영양식</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12044048136</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958855/89588558835.jpg</t>
-  </si>
-  <si>
-    <t>힐링짱</t>
-  </si>
-  <si>
-    <t>NEW&lt;b&gt;포켄스&lt;/b&gt; 카누들 덴탈껌 S 100p 1+1 -</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043920449</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958843/89588431148.jpg</t>
-  </si>
-  <si>
-    <t>클린Health</t>
-  </si>
-  <si>
-    <t>고양이 간식</t>
-  </si>
-  <si>
-    <t>동결건조 간식</t>
-  </si>
-  <si>
-    <t>덴티페어리 벌크팩 SS 217개입 1.02kg &lt;b&gt;포켄스&lt;/b&gt; 강아지덴탈껌 치석 입냄새 감소 높은 기호성</t>
-  </si>
-  <si>
-    <t>https://link.auction.co.kr/gate/pcs?item-no=F264376267&amp;sub-id=1&amp;service-code=10000003</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5557943/55579432858.jpg</t>
-  </si>
-  <si>
-    <t>https://link.gmarket.co.kr/gate/pcs?item-no=4149710046&amp;sub-id=1003&amp;service-code=10000003&amp;lcd=100000038</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5557938/55579386777.jpg</t>
-  </si>
-  <si>
-    <t>서락 &lt;b&gt;포켄스&lt;/b&gt; 덴티 페어리 65g 입냄세제거 대형견개껌 강아지껌 강아지간식</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043630283</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958814/89588140982.jpg</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;포켄스&lt;/b&gt; 덴티 페어리 65g (S) (강아지 간식)</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043833423</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958834/89588344122.jpg</t>
-  </si>
-  <si>
-    <t>아르덴랜드</t>
-  </si>
-  <si>
-    <t>서락 &lt;b&gt;포켄스&lt;/b&gt; 과일먹은 치즈덴탈껌 딸기 맛있는간식 애견과일껌 맛좋은강아지간식</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043805235</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958831/89588315934.jpg</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;포켄스&lt;/b&gt; 화이트닝 샴푸 1000ml 선택</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043794418</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958830/89588305117.jpg</t>
-  </si>
-  <si>
-    <t>샴푸/린스/비누</t>
-  </si>
-  <si>
-    <t>https://smartstore.naver.com/main/products/12043693959</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_8958820/89588204658.jpg</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;포켄스&lt;/b&gt; 뉴트리션 트릿 면역 영양 240g관 보충 저키 강아지져 져키</t>
-  </si>
-  <si>
-    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=8431919085&amp;tid=1000000061</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5557930/55579303499.jpg</t>
-  </si>
-  <si>
-    <t>11번가</t>
-  </si>
-  <si>
-    <t>트릿/스틱</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;포켄스&lt;/b&gt; 덴티페어리 SS 디스펜서 (124p) 강아지 덴탈껌</t>
-  </si>
-  <si>
-    <t>https://www.11st.co.kr/connect/Gateway.tmall?method=Xsite&amp;prdNo=7898487960&amp;tid=1000000061</t>
-  </si>
-  <si>
-    <t>https://shopping-phinf.pstatic.net/main_5557929/55579294213.jpg</t>
-  </si>
-  <si>
-    <t>페슬러</t>
-  </si>
-  <si>
-    <t>2025-07-01 17:20:33 기준</t>
+    <t>2025-07-01 17:53:47 기준</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>최근 목록은 반려동물 배변용품·간식 중심에서 치과용품(덴티페어리), 미용샴푸, 청소용품 등 건강관리와 위생 용품으로 대체되었으며, 상품 가격은 1,100원부터 69,400원까지 다양해졌고, 쇼핑몰도 변경되어 옥션·G마켓·11번가 등으로 다변화됐습니다.</t>
+    <t>두 목록 모두 포켄스 덴탈스틱 후레시 칼슘(220g)이 상위권에 유지되었으며, 가격은 10990원으로 동일합니다. 그러나 now_list에서 포켄스 덴티페어리 베트 VET 70g가 실물 사진과 가격 정보가 추가돼 상품 다양성이 높아졌고, 일부 품목에는 하이퍼링크, 판매처와 제품정보가 구체적으로 표기되어 경쟁력 있는 상품 구성이 강화된 특징이 드러납니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 포켄스(FORCANS)는 2025년 3월 7일, 소형견 맞춤 '미니바이츠' 덴탈껌(사이즈 S, SS) 2종을 출시. 
-- 고객 관찰 분석 후 별도 쪼갤 필요 없이 370개 제품 판매로 인기.
-- 온라인 할인 행사와 이벤트 통해 제품 판매 촉진, 2024년부터 마케팅 전략 강화.</t>
+    <t>- 포켄스, 3월 7일 소형견 맞춤 ‘미니바이츠’ 덴탈껌 2종(SS, S)를 출시하였다.  
+- 연구소 관찰 후 별도 쪼개기 필요 없는 20g 미니 크기.  
+- 현재 온라인 할인 행사 및 브랜드 타임세일 통해 판매 중.  
+- 제품 판매량 및 광고 효율 향상 위해 ‘에이아이웹’ 퍼포먼스 마케팅 활용.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1160,7 +870,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
-        <v>198</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
@@ -1168,9 +878,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="57.6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:1" ht="76.8" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
-        <v>199</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -1181,7 +891,7 @@
     </row>
     <row r="8" spans="1:1" s="3" customFormat="1" ht="76.8" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
-        <v>200</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1192,7 +902,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84332D04-46BF-4775-A676-AFD08174531A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4870D394-8404-47FA-AF09-D2BA64C825A9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1209,7 +919,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
@@ -1217,9 +927,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="19.2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:1" ht="57.6" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -1228,9 +938,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:1" s="3" customFormat="1" ht="115.2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:1" s="3" customFormat="1" ht="96" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1253,33 +963,33 @@
   <sheetData>
     <row r="1" spans="1:1" ht="36" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="384" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="7" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:1" s="3" customFormat="1" ht="230.4" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1346,22 +1056,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="E2">
-        <v>34700</v>
+        <v>10990</v>
       </c>
       <c r="G2" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="H2">
-        <v>55579876708</v>
+        <v>55580027908</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -1373,10 +1083,10 @@
         <v>19</v>
       </c>
       <c r="N2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O2" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
@@ -1384,22 +1094,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>137</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>69400</v>
+        <v>34700</v>
       </c>
       <c r="G3" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="H3">
-        <v>55579859939</v>
+        <v>55579876708</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -1411,10 +1121,10 @@
         <v>19</v>
       </c>
       <c r="N3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O3" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.4">
@@ -1422,22 +1132,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>38</v>
       </c>
       <c r="E4">
-        <v>18200</v>
+        <v>69400</v>
       </c>
       <c r="G4" t="s">
-        <v>138</v>
+        <v>39</v>
       </c>
       <c r="H4">
-        <v>55579843217</v>
+        <v>55579859939</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -1449,10 +1159,10 @@
         <v>19</v>
       </c>
       <c r="N4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O4" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.4">
@@ -1460,22 +1170,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="E5">
-        <v>18300</v>
+        <v>18200</v>
       </c>
       <c r="G5" t="s">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="H5">
-        <v>55579837623</v>
+        <v>55579843217</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -1487,10 +1197,10 @@
         <v>19</v>
       </c>
       <c r="N5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O5" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.4">
@@ -1498,22 +1208,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>145</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>44</v>
       </c>
       <c r="E6">
-        <v>34400</v>
+        <v>18300</v>
       </c>
       <c r="G6" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="H6">
-        <v>55579825410</v>
+        <v>55579837623</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -1525,10 +1235,10 @@
         <v>19</v>
       </c>
       <c r="N6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O6" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.4">
@@ -1536,22 +1246,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="E7">
-        <v>34700</v>
+        <v>34400</v>
       </c>
       <c r="G7" t="s">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="H7">
-        <v>55579797058</v>
+        <v>55579825410</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -1563,10 +1273,10 @@
         <v>19</v>
       </c>
       <c r="N7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O7" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.4">
@@ -1574,22 +1284,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="E8">
-        <v>70100</v>
+        <v>34700</v>
       </c>
       <c r="G8" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="H8">
-        <v>55579793345</v>
+        <v>55579797058</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -1601,10 +1311,10 @@
         <v>19</v>
       </c>
       <c r="N8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O8" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
@@ -1612,22 +1322,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="E9">
-        <v>34400</v>
+        <v>70100</v>
       </c>
       <c r="G9" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="H9">
-        <v>55579791835</v>
+        <v>55579793345</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -1639,10 +1349,10 @@
         <v>19</v>
       </c>
       <c r="N9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O9" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.4">
@@ -1650,32 +1360,26 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>153</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>154</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>53</v>
       </c>
       <c r="E10">
-        <v>20300</v>
+        <v>34400</v>
       </c>
       <c r="G10" t="s">
-        <v>156</v>
+        <v>39</v>
       </c>
       <c r="H10">
-        <v>89588574489</v>
+        <v>55579791835</v>
       </c>
       <c r="I10">
         <v>2</v>
       </c>
-      <c r="J10" t="s">
-        <v>157</v>
-      </c>
-      <c r="K10" t="s">
-        <v>157</v>
-      </c>
       <c r="L10" t="s">
         <v>18</v>
       </c>
@@ -1683,7 +1387,10 @@
         <v>19</v>
       </c>
       <c r="N10" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="O10" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.4">
@@ -1691,26 +1398,32 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="E11">
-        <v>6940</v>
+        <v>20300</v>
       </c>
       <c r="G11" t="s">
-        <v>161</v>
+        <v>57</v>
       </c>
       <c r="H11">
-        <v>89588558835</v>
+        <v>89588574489</v>
       </c>
       <c r="I11">
         <v>2</v>
       </c>
+      <c r="J11" t="s">
+        <v>58</v>
+      </c>
+      <c r="K11" t="s">
+        <v>58</v>
+      </c>
       <c r="L11" t="s">
         <v>18</v>
       </c>
@@ -1718,10 +1431,7 @@
         <v>19</v>
       </c>
       <c r="N11" t="s">
-        <v>29</v>
-      </c>
-      <c r="O11" t="s">
-        <v>134</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.4">
@@ -1729,32 +1439,26 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>162</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>163</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
-        <v>164</v>
+        <v>61</v>
       </c>
       <c r="E12">
-        <v>67400</v>
+        <v>6940</v>
       </c>
       <c r="G12" t="s">
-        <v>165</v>
+        <v>62</v>
       </c>
       <c r="H12">
-        <v>89588431148</v>
+        <v>89588558835</v>
       </c>
       <c r="I12">
         <v>2</v>
       </c>
-      <c r="J12" t="s">
-        <v>157</v>
-      </c>
-      <c r="K12" t="s">
-        <v>157</v>
-      </c>
       <c r="L12" t="s">
         <v>18</v>
       </c>
@@ -1762,10 +1466,10 @@
         <v>19</v>
       </c>
       <c r="N12" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
       <c r="O12" t="s">
-        <v>167</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.4">
@@ -1773,26 +1477,32 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>169</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="E13">
-        <v>72000</v>
+        <v>67400</v>
       </c>
       <c r="G13" t="s">
-        <v>133</v>
+        <v>66</v>
       </c>
       <c r="H13">
-        <v>55579432858</v>
+        <v>89588431148</v>
       </c>
       <c r="I13">
         <v>2</v>
       </c>
+      <c r="J13" t="s">
+        <v>58</v>
+      </c>
+      <c r="K13" t="s">
+        <v>58</v>
+      </c>
       <c r="L13" t="s">
         <v>18</v>
       </c>
@@ -1800,10 +1510,10 @@
         <v>19</v>
       </c>
       <c r="N13" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="O13" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.4">
@@ -1811,22 +1521,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>168</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>171</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
-        <v>172</v>
+        <v>71</v>
       </c>
       <c r="E14">
-        <v>64080</v>
+        <v>72000</v>
       </c>
       <c r="G14" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="H14">
-        <v>55579386777</v>
+        <v>55579432858</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -1838,10 +1548,10 @@
         <v>19</v>
       </c>
       <c r="N14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O14" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.4">
@@ -1849,22 +1559,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>173</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>175</v>
+        <v>73</v>
       </c>
       <c r="E15">
-        <v>4920</v>
+        <v>64080</v>
       </c>
       <c r="G15" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H15">
-        <v>89588140982</v>
+        <v>55579386777</v>
       </c>
       <c r="I15">
         <v>2</v>
@@ -1876,10 +1586,10 @@
         <v>19</v>
       </c>
       <c r="N15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O15" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.4">
@@ -1887,22 +1597,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>176</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>177</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>178</v>
+        <v>76</v>
       </c>
       <c r="E16">
-        <v>11490</v>
+        <v>4920</v>
       </c>
       <c r="G16" t="s">
-        <v>179</v>
+        <v>30</v>
       </c>
       <c r="H16">
-        <v>89588344122</v>
+        <v>89588140982</v>
       </c>
       <c r="I16">
         <v>2</v>
@@ -1914,10 +1624,10 @@
         <v>19</v>
       </c>
       <c r="N16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O16" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.4">
@@ -1925,22 +1635,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>182</v>
+        <v>79</v>
       </c>
       <c r="E17">
-        <v>3360</v>
+        <v>11490</v>
       </c>
       <c r="G17" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="H17">
-        <v>89588315934</v>
+        <v>89588344122</v>
       </c>
       <c r="I17">
         <v>2</v>
@@ -1952,10 +1662,10 @@
         <v>19</v>
       </c>
       <c r="N17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O17" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.4">
@@ -1963,32 +1673,26 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>183</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>185</v>
+        <v>83</v>
       </c>
       <c r="E18">
-        <v>18170</v>
+        <v>3360</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H18">
-        <v>89588305117</v>
+        <v>89588315934</v>
       </c>
       <c r="I18">
         <v>2</v>
       </c>
-      <c r="J18" t="s">
-        <v>157</v>
-      </c>
-      <c r="K18" t="s">
-        <v>157</v>
-      </c>
       <c r="L18" t="s">
         <v>18</v>
       </c>
@@ -1996,10 +1700,10 @@
         <v>19</v>
       </c>
       <c r="N18" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="O18" t="s">
-        <v>186</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.4">
@@ -2007,26 +1711,32 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>187</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>188</v>
+        <v>86</v>
       </c>
       <c r="E19">
-        <v>11780</v>
+        <v>18170</v>
       </c>
       <c r="G19" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H19">
-        <v>89588204658</v>
+        <v>89588305117</v>
       </c>
       <c r="I19">
         <v>2</v>
       </c>
+      <c r="J19" t="s">
+        <v>58</v>
+      </c>
+      <c r="K19" t="s">
+        <v>58</v>
+      </c>
       <c r="L19" t="s">
         <v>18</v>
       </c>
@@ -2034,10 +1744,10 @@
         <v>19</v>
       </c>
       <c r="N19" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="O19" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.4">
@@ -2045,22 +1755,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>190</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
-        <v>191</v>
+        <v>89</v>
       </c>
       <c r="E20">
-        <v>19610</v>
+        <v>11780</v>
       </c>
       <c r="G20" t="s">
-        <v>192</v>
+        <v>29</v>
       </c>
       <c r="H20">
-        <v>55579303499</v>
+        <v>89588204658</v>
       </c>
       <c r="I20">
         <v>2</v>
@@ -2072,10 +1782,10 @@
         <v>19</v>
       </c>
       <c r="N20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O20" t="s">
-        <v>193</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.4">
@@ -2083,29 +1793,26 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>194</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>195</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s">
-        <v>196</v>
+        <v>92</v>
       </c>
       <c r="E21">
-        <v>44160</v>
+        <v>19610</v>
       </c>
       <c r="G21" t="s">
-        <v>192</v>
+        <v>93</v>
       </c>
       <c r="H21">
-        <v>55579294213</v>
+        <v>55579303499</v>
       </c>
       <c r="I21">
         <v>2</v>
       </c>
-      <c r="J21" t="s">
-        <v>197</v>
-      </c>
       <c r="L21" t="s">
         <v>18</v>
       </c>
@@ -2113,10 +1820,10 @@
         <v>19</v>
       </c>
       <c r="N21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O21" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2126,7 +1833,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AC6ED0-1D7D-410B-8E53-3876EC6F573C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ADA8C96-D8CA-4CD7-B395-49AF5F8647B2}">
   <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -2182,22 +1889,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="E2">
-        <v>57480</v>
+        <v>10990</v>
       </c>
       <c r="G2" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="H2">
-        <v>89588404320</v>
+        <v>55580027908</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -2209,10 +1916,10 @@
         <v>19</v>
       </c>
       <c r="N2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="O2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
@@ -2220,22 +1927,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>15000</v>
+        <v>34700</v>
       </c>
       <c r="G3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="H3">
-        <v>89588437193</v>
+        <v>55579876708</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -2247,7 +1954,10 @@
         <v>19</v>
       </c>
       <c r="N3" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="O3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.4">
@@ -2255,29 +1965,26 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E4">
-        <v>2130</v>
+        <v>69400</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H4">
-        <v>89588314106</v>
+        <v>55579859939</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
-      <c r="K4" t="s">
-        <v>50</v>
-      </c>
       <c r="L4" t="s">
         <v>18</v>
       </c>
@@ -2285,10 +1992,10 @@
         <v>19</v>
       </c>
       <c r="N4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="O4" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.4">
@@ -2296,22 +2003,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E5">
-        <v>1880</v>
+        <v>18200</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H5">
-        <v>89588436097</v>
+        <v>55579843217</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -2323,10 +2030,10 @@
         <v>19</v>
       </c>
       <c r="N5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="O5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.4">
@@ -2334,22 +2041,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="E6">
-        <v>5780</v>
+        <v>18300</v>
       </c>
       <c r="G6" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="H6">
-        <v>89588435755</v>
+        <v>55579837623</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -2361,10 +2068,10 @@
         <v>19</v>
       </c>
       <c r="N6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.4">
@@ -2372,29 +2079,26 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E7">
-        <v>2000</v>
+        <v>34400</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H7">
-        <v>89588305151</v>
+        <v>55579825410</v>
       </c>
       <c r="I7">
         <v>2</v>
       </c>
-      <c r="K7" t="s">
-        <v>36</v>
-      </c>
       <c r="L7" t="s">
         <v>18</v>
       </c>
@@ -2402,10 +2106,10 @@
         <v>19</v>
       </c>
       <c r="N7" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="O7" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.4">
@@ -2413,29 +2117,26 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="E8">
-        <v>8380</v>
+        <v>34700</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="H8">
-        <v>89588433170</v>
+        <v>55579797058</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
-      <c r="K8" t="s">
-        <v>67</v>
-      </c>
       <c r="L8" t="s">
         <v>18</v>
       </c>
@@ -2443,7 +2144,10 @@
         <v>19</v>
       </c>
       <c r="N8" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="O8" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
@@ -2451,22 +2155,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="E9">
-        <v>51900</v>
+        <v>70100</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H9">
-        <v>89588433426</v>
+        <v>55579793345</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -2478,10 +2182,10 @@
         <v>19</v>
       </c>
       <c r="N9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O9" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.4">
@@ -2489,22 +2193,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="E10">
-        <v>9900</v>
+        <v>34400</v>
       </c>
       <c r="G10" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="H10">
-        <v>89588302111</v>
+        <v>55579791835</v>
       </c>
       <c r="I10">
         <v>2</v>
@@ -2513,13 +2217,13 @@
         <v>18</v>
       </c>
       <c r="M10" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="N10" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="O10" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.4">
@@ -2527,25 +2231,31 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="E11">
-        <v>76330</v>
+        <v>20300</v>
       </c>
       <c r="G11" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="H11">
-        <v>89588432654</v>
+        <v>89588574489</v>
       </c>
       <c r="I11">
         <v>2</v>
+      </c>
+      <c r="J11" t="s">
+        <v>58</v>
+      </c>
+      <c r="K11" t="s">
+        <v>58</v>
       </c>
       <c r="L11" t="s">
         <v>18</v>
@@ -2562,22 +2272,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="E12">
-        <v>16000</v>
+        <v>6940</v>
       </c>
       <c r="G12" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="H12">
-        <v>89588431561</v>
+        <v>89588558835</v>
       </c>
       <c r="I12">
         <v>2</v>
@@ -2589,7 +2299,10 @@
         <v>19</v>
       </c>
       <c r="N12" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="O12" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.4">
@@ -2597,28 +2310,31 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="E13">
-        <v>16650</v>
+        <v>67400</v>
       </c>
       <c r="G13" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="H13">
-        <v>89588431280</v>
+        <v>89588431148</v>
       </c>
       <c r="I13">
         <v>2</v>
       </c>
+      <c r="J13" t="s">
+        <v>58</v>
+      </c>
       <c r="K13" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="L13" t="s">
         <v>18</v>
@@ -2627,10 +2343,10 @@
         <v>19</v>
       </c>
       <c r="N13" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="O13" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.4">
@@ -2638,22 +2354,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="E14">
-        <v>5500</v>
+        <v>72000</v>
       </c>
       <c r="G14" t="s">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="H14">
-        <v>89588388722</v>
+        <v>55579432858</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -2665,7 +2381,10 @@
         <v>19</v>
       </c>
       <c r="N14" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="O14" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.4">
@@ -2673,22 +2392,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="E15">
-        <v>60120</v>
+        <v>64080</v>
       </c>
       <c r="G15" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="H15">
-        <v>89588430610</v>
+        <v>55579386777</v>
       </c>
       <c r="I15">
         <v>2</v>
@@ -2700,10 +2419,10 @@
         <v>19</v>
       </c>
       <c r="N15" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="O15" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.4">
@@ -2711,22 +2430,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="E16">
-        <v>11700</v>
+        <v>4920</v>
       </c>
       <c r="G16" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="H16">
-        <v>89588429695</v>
+        <v>89588140982</v>
       </c>
       <c r="I16">
         <v>2</v>
@@ -2738,10 +2457,10 @@
         <v>19</v>
       </c>
       <c r="N16" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="O16" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.4">
@@ -2749,22 +2468,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="E17">
-        <v>237800</v>
+        <v>11490</v>
       </c>
       <c r="G17" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="H17">
-        <v>89588429526</v>
+        <v>89588344122</v>
       </c>
       <c r="I17">
         <v>2</v>
@@ -2773,10 +2492,13 @@
         <v>18</v>
       </c>
       <c r="M17" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="N17" t="s">
-        <v>111</v>
+        <v>28</v>
+      </c>
+      <c r="O17" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.4">
@@ -2784,22 +2506,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E18">
-        <v>1080</v>
+        <v>3360</v>
       </c>
       <c r="G18" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="H18">
-        <v>89588429160</v>
+        <v>89588315934</v>
       </c>
       <c r="I18">
         <v>2</v>
@@ -2811,10 +2533,10 @@
         <v>19</v>
       </c>
       <c r="N18" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="O18" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.4">
@@ -2822,25 +2544,31 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="E19">
-        <v>1570</v>
+        <v>18170</v>
       </c>
       <c r="G19" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="H19">
-        <v>89588429164</v>
+        <v>89588305117</v>
       </c>
       <c r="I19">
         <v>2</v>
+      </c>
+      <c r="J19" t="s">
+        <v>58</v>
+      </c>
+      <c r="K19" t="s">
+        <v>58</v>
       </c>
       <c r="L19" t="s">
         <v>18</v>
@@ -2852,7 +2580,7 @@
         <v>20</v>
       </c>
       <c r="O19" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.4">
@@ -2860,22 +2588,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="E20">
-        <v>1570</v>
+        <v>11780</v>
       </c>
       <c r="G20" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="H20">
-        <v>89588429161</v>
+        <v>89588204658</v>
       </c>
       <c r="I20">
         <v>2</v>
@@ -2887,10 +2615,10 @@
         <v>19</v>
       </c>
       <c r="N20" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="O20" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.4">
@@ -2898,22 +2626,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="E21">
-        <v>890</v>
+        <v>19610</v>
       </c>
       <c r="G21" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="H21">
-        <v>89588429167</v>
+        <v>55579303499</v>
       </c>
       <c r="I21">
         <v>2</v>
@@ -2925,10 +2653,10 @@
         <v>19</v>
       </c>
       <c r="N21" t="s">
-        <v>125</v>
+        <v>28</v>
       </c>
       <c r="O21" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
